--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.4.25</t>
+    <t>日期: 2026.4.26</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>28-38</t>
+    <t>35-38</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-12</t>
+    <t>9.5-11</t>
   </si>
   <si>
     <t>4</t>
@@ -83,15 +83,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>9.5-10.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-9.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -110,16 +113,13 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-11.5</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂货类批发价格:</t>
+    <t>杂 货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
@@ -137,7 +137,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-58</t>
+    <t>20-55</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -146,13 +146,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.5-7.2</t>
+    <t>6.7-7.2</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>30-57</t>
+    <t>30-58</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -197,43 +197,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>140</t>
+    <t>150</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-21-17</t>
+    <t>22-20-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>123</t>
+    <t>120</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>60-43-32</t>
+    <t>70-58-42</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>103</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>46-37-25</t>
+    <t>46-37-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>91</t>
+    <t>90</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -260,7 +260,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>26-29</t>
+    <t>28-32</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -269,7 +269,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>11-13</t>
+    <t>14-16</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -278,7 +278,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>8-16</t>
   </si>
 </sst>
 </file>
@@ -1879,7 +1879,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2019,40 +2019,40 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="54" t="s">
         <v>28</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="10.0" customHeight="true">
+    <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
         <v>35</v>
       </c>
@@ -2179,25 +2179,25 @@
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>53</v>
@@ -2206,7 +2206,7 @@
         <v>54</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
         <v>55</v>
@@ -2215,7 +2215,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="14.0" customHeight="true">
+    <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
         <v>33</v>
       </c>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="F20" s="120"/>
     </row>
-    <row r="21" ht="10.0" customHeight="true">
+    <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
         <v>59</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" ht="14.0" customHeight="true">
+    <row r="24" ht="10.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>75</v>
@@ -2350,7 +2350,7 @@
         <v>76</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>77</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
         <v>80</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.4.26</t>
+    <t>日期: 2026.4.27</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -137,7 +137,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-55</t>
+    <t>20-57</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -158,30 +158,30 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
+    <t>蛳 螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>鲴鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
+    <t>8.5-12</t>
+  </si>
+  <si>
+    <t>昂 刺鱼</t>
+  </si>
+  <si>
     <t>10-13</t>
   </si>
   <si>
-    <t>蛳 螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-6</t>
-  </si>
-  <si>
-    <t>鲴鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
-    <t>8.5-12</t>
-  </si>
-  <si>
-    <t>昂 刺鱼</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -197,43 +197,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>150</t>
+    <t>140</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-16</t>
+    <t>22-20-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>120</t>
+    <t>118</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58-42</t>
+    <t>68-49-35</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>103</t>
+    <t>97</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>46-37-28</t>
+    <t>43-37-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>86</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -242,7 +242,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>73</t>
+    <t>70</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -260,7 +260,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>28-32</t>
+    <t>26-28</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -269,7 +269,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>14-16</t>
+    <t>9-12</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -278,7 +278,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-16</t>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -2165,16 +2165,16 @@
         <v>47</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>49</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2182,14 +2182,14 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>30</v>
@@ -2200,19 +2200,19 @@
         <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>54</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>55</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="88">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.4.27</t>
+    <t>日期: 2026.4.28</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-38</t>
+    <t>30-38</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>9.5-12</t>
   </si>
   <si>
     <t>4</t>
@@ -83,13 +83,13 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>6</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
+    <t>9.5-10</t>
   </si>
   <si>
     <t>5</t>
@@ -104,15 +104,15 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>红鱼</t>
   </si>
   <si>
     <t>青鱼</t>
   </si>
   <si>
+    <t>10.5-11</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -179,9 +179,6 @@
     <t>昂 刺鱼</t>
   </si>
   <si>
-    <t>10-13</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -197,43 +194,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>140</t>
+    <t>130</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-15</t>
+    <t>22-21-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>110</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>68-49-35</t>
+    <t>70-57-38</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>97</t>
+    <t>92</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>43-37-26</t>
+    <t>41-35-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>86</t>
+    <t>80</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -242,7 +239,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>63</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -260,7 +257,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>26-28</t>
+    <t>25-28</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -269,7 +266,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-12</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -2039,20 +2036,20 @@
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
@@ -2192,12 +2189,12 @@
         <v>51</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>52</v>
@@ -2206,13 +2203,13 @@
         <v>53</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E19" s="113" t="s">
         <v>54</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2220,20 +2217,20 @@
         <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>57</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2266,19 +2263,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>60</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>61</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>62</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2286,19 +2283,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>64</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>65</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>66</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2306,19 +2303,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>68</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>69</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>70</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2326,16 +2323,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>72</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>73</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2344,22 +2341,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>75</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>76</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2375,7 +2372,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2388,13 +2385,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>81</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>82</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2404,10 +2401,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2418,13 +2415,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>84</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>85</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2434,10 +2431,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2448,13 +2445,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>87</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.4.28</t>
+    <t>日期: 2026.4.29</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,120 +44,126 @@
     <t>鲫鱼</t>
   </si>
   <si>
+    <t>8-14</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>鳜鱼(桂鱼)</t>
+  </si>
+  <si>
+    <t>30-38</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>4-4.5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂 货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>37-48</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-58</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>6.8-7.3</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>30-57</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
     <t>10-14</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>鳜鱼(桂鱼)</t>
-  </si>
-  <si>
-    <t>30-38</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>4-4.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-15</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>9.5-12</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>9.5-10</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>10.5-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂 货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-48</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-57</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>6.7-7.2</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>30-58</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
     <t>蛳 螺(养殖)</t>
   </si>
   <si>
@@ -173,12 +179,15 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>8.5-12</t>
+    <t>8.5-12.5</t>
   </si>
   <si>
     <t>昂 刺鱼</t>
   </si>
   <si>
+    <t>10-13</t>
+  </si>
+  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -194,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>130</t>
+    <t>118</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-21-15</t>
+    <t>22-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>110</t>
+    <t>102</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-57-38</t>
+    <t>70-58-35</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>92</t>
+    <t>87</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>41-35-27</t>
+    <t>40-33-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>80</t>
+    <t>70</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -239,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>63</t>
+    <t>55</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -257,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>25-28</t>
+    <t>27-30</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -266,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>11-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -275,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>7-9</t>
   </si>
 </sst>
 </file>
@@ -2031,44 +2040,44 @@
         <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2101,19 +2110,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2121,16 +2130,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2139,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2159,19 +2168,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2179,58 +2188,58 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2263,19 +2272,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2283,19 +2292,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2303,19 +2312,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2323,16 +2332,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2341,22 +2350,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2372,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2385,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2401,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2415,13 +2424,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2431,10 +2440,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2445,13 +2454,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.4.29</t>
+    <t>日期: 2026.4.30</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>2</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8.5-10</t>
+    <t>8.5-9</t>
   </si>
   <si>
     <t>5</t>
@@ -98,9 +98,6 @@
     <t>非洲鲫鱼</t>
   </si>
   <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
     <t>鳊鱼</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
     <t>青鱼</t>
   </si>
   <si>
+    <t>8.5-11</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-58</t>
+    <t>20-57</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -161,9 +161,6 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>10-14</t>
-  </si>
-  <si>
     <t>蛳 螺(养殖)</t>
   </si>
   <si>
@@ -179,7 +176,7 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>8.5-12.5</t>
+    <t>8.5-12</t>
   </si>
   <si>
     <t>昂 刺鱼</t>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>125</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-17</t>
+    <t>22-20-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>108</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58-35</t>
+    <t>70-58-34</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>83</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-33-27</t>
+    <t>42-37-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>72</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>55</t>
+    <t>58</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,16 +263,13 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>27-30</t>
+    <t>25-28</t>
   </si>
   <si>
     <t>7-9红</t>
   </si>
   <si>
     <t>4-6青</t>
-  </si>
-  <si>
-    <t>11-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -2031,34 +2025,34 @@
         <v>27</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
@@ -2171,16 +2165,16 @@
         <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2188,37 +2182,37 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="D19" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2226,20 +2220,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2266,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2292,19 +2286,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2306,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2332,16 +2326,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2350,22 +2344,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2388,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,10 +2404,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,13 +2418,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2434,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2448,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.4.30</t>
+    <t>日期:2026.5.2</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>30-38</t>
+    <t>33-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -89,15 +89,18 @@
     <t>花鲢</t>
   </si>
   <si>
+    <t>9-10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
     <t>8.5-9</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
     <t>鳊鱼</t>
   </si>
   <si>
@@ -113,7 +116,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-11</t>
+    <t>8.5-10</t>
   </si>
   <si>
     <t>7</t>
@@ -122,7 +125,7 @@
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂 货类批发价格:</t>
+    <t>杂货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
@@ -149,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.8-7.3</t>
+    <t>6.7-7.3</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -161,13 +164,13 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>蛳 螺(养殖)</t>
+    <t>蛳螺(养殖)</t>
   </si>
   <si>
     <t>3-6</t>
   </si>
   <si>
-    <t>鲴鱼</t>
+    <t>鮰鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -179,7 +182,7 @@
     <t>8.5-12</t>
   </si>
   <si>
-    <t>昂 刺鱼</t>
+    <t>昂刺鱼</t>
   </si>
   <si>
     <t>10-13</t>
@@ -200,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>125</t>
+    <t>150</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-16</t>
+    <t>23-21-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>129</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58-34</t>
+    <t>72-58-32</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>83</t>
+    <t>110</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-37-28</t>
+    <t>44-37-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>72</t>
+    <t>82</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>58</t>
+    <t>62</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -263,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>25-28</t>
+    <t>26-28</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -272,13 +275,16 @@
     <t>4-6青</t>
   </si>
   <si>
+    <t>11-14</t>
+  </si>
+  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -1879,7 +1885,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -1887,7 +1893,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1903,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="12.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1957,7 +1963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="14.0" customHeight="true">
+    <row r="6" ht="10.0" customHeight="true">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2025,53 +2031,53 @@
         <v>27</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="14.0" customHeight="true">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="14.0" customHeight="true">
+    <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2104,36 +2110,36 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" ht="14.0" customHeight="true">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="10.0" customHeight="true">
       <c r="A15" s="85" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2142,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2162,7 +2168,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
         <v>10</v>
@@ -2171,10 +2177,10 @@
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2182,58 +2188,58 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="10.0" customHeight="true">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2266,39 +2272,39 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" ht="10.0" customHeight="true">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="14.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2306,60 +2312,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" ht="14.0" customHeight="true">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="10.0" customHeight="true">
       <c r="A26" s="151" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="14.0" customHeight="true">
+    <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2375,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2388,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2404,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2418,43 +2424,43 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="10.0" customHeight="true">
+    <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
       <c r="F33" s="198"/>
     </row>
-    <row r="34" ht="10.0" customHeight="true">
+    <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2472,7 +2478,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.2</t>
+    <t>日期:2026.5.3</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>33-37</t>
+    <t>28-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -83,13 +83,13 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>6</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
-    <t>9-10</t>
+    <t>8.5-10</t>
   </si>
   <si>
     <t>5</t>
@@ -107,18 +107,12 @@
     <t>8-9</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>红鱼</t>
   </si>
   <si>
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-10</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -143,7 +137,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-57</t>
+    <t>20-58</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -152,13 +146,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.7-7.3</t>
+    <t>6.9-7.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>30-57</t>
+    <t>30-59</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -203,19 +197,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>150</t>
+    <t>138</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>23-21-17</t>
+    <t>23-20-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>129</t>
+    <t>112</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,13 +221,13 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>110</t>
+    <t>96</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>44-37-30</t>
+    <t>44-35-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -248,7 +242,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>62</t>
+    <t>63</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +260,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>26-28</t>
+    <t>27-29</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +269,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>11-14</t>
+    <t>11-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -2045,39 +2039,39 @@
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2110,19 +2104,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="10.0" customHeight="true">
@@ -2130,16 +2124,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2148,19 +2142,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2168,7 +2162,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="99" t="s">
         <v>10</v>
@@ -2177,10 +2171,10 @@
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2188,58 +2182,58 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="F19" s="114" t="s">
         <v>55</v>
-      </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2266,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2292,19 +2286,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2306,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2332,16 +2326,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2350,22 +2344,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2388,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="177" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="178" t="s">
         <v>82</v>
-      </c>
-      <c r="C30" s="177" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,10 +2404,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,13 +2418,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2434,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2448,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.3</t>
+    <t>日期:2026.5.4</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -125,7 +125,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>37-48</t>
+    <t>35-47</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -146,7 +146,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.9-7.5</t>
+    <t>6.7-7.2</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -197,43 +197,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>138</t>
+    <t>125</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>23-20-16</t>
+    <t>21-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>112</t>
+    <t>108</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-58-32</t>
+    <t>70-58-39</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>96</t>
+    <t>92</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>44-35-26</t>
+    <t>45-37-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>82</t>
+    <t>83</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -242,7 +242,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>63</t>
+    <t>68</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -260,7 +260,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>27-29</t>
+    <t>27-30</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -269,7 +269,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>11-13</t>
+    <t>12-15</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -278,7 +278,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>9-11</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1887,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="12.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2413,7 +2413,7 @@
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="14.0" customHeight="true">
+    <row r="32" ht="10.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.4</t>
+    <t>日期:2026.5.5</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,120 +44,126 @@
     <t>鲫鱼</t>
   </si>
   <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>鳜鱼(桂鱼)</t>
+  </si>
+  <si>
+    <t>30-37</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>4-4.5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9.5-10</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-47</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-58</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>6.7-7.2</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>30-59</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
     <t>10-14</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>鳜鱼(桂鱼)</t>
-  </si>
-  <si>
-    <t>28-37</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>4-4.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-15</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>9.5-11</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-10</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-47</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-58</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>6.7-7.2</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>30-59</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
     <t>蛳螺(养殖)</t>
   </si>
   <si>
@@ -197,13 +203,13 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>125</t>
+    <t>130</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>21-20-17</t>
+    <t>23-22-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
@@ -215,7 +221,7 @@
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58-39</t>
+    <t>70-58-40</t>
   </si>
   <si>
     <t>河虾(150头)</t>
@@ -233,7 +239,7 @@
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>83</t>
+    <t>85</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -242,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>67</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -260,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>27-30</t>
+    <t>26-29</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -269,16 +275,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-15</t>
-  </si>
-  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>7-9</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1890,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1900,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="12.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1985,93 +1988,93 @@
         <v>17</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D7" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="42" t="s">
         <v>19</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" ht="14.0" customHeight="true">
       <c r="A8" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="C8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="D8" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="47" t="s">
+      <c r="F8" s="48" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2104,19 +2107,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="10.0" customHeight="true">
@@ -2124,16 +2127,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2142,98 +2145,98 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
       <c r="A17" s="97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2266,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2286,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2306,60 +2309,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
       <c r="A26" s="151" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2375,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2388,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2404,40 +2407,40 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="10.0" customHeight="true">
+    <row r="32" ht="14.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
     <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2445,16 +2448,16 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.5</t>
+    <t>日期:2026.5.6</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,30 +44,33 @@
     <t>鲫鱼</t>
   </si>
   <si>
+    <t>8-15</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>鳜鱼(桂鱼)</t>
+  </si>
+  <si>
+    <t>33-38</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>4-4.5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
     <t>10-15</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>鳜鱼(桂鱼)</t>
-  </si>
-  <si>
-    <t>30-37</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>4-4.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
     <t>草鱼</t>
   </si>
   <si>
@@ -113,7 +116,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-10</t>
+    <t>9-10</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-47</t>
+    <t>38-47</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-58</t>
+    <t>20-57</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,13 +152,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.7-7.2</t>
+    <t>6.8-7.3</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>30-59</t>
+    <t>30-57</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -167,7 +170,7 @@
     <t>蛳螺(养殖)</t>
   </si>
   <si>
-    <t>3-6</t>
+    <t>3-5.5</t>
   </si>
   <si>
     <t>鮰鱼</t>
@@ -203,19 +206,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>130</t>
+    <t>118</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>23-22-17</t>
+    <t>22-21-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>102</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,19 +230,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>92</t>
+    <t>87</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>45-37-30</t>
+    <t>42-36-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>85</t>
+    <t>78</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +251,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>67</t>
+    <t>60</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>26-29</t>
+    <t>23-29</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,13 +278,16 @@
     <t>4-6青</t>
   </si>
   <si>
+    <t>8-11</t>
+  </si>
+  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1896,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1900,7 +1906,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="12.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1988,93 +1994,93 @@
         <v>17</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D7" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="14.0" customHeight="true">
       <c r="A8" s="43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2113,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="10.0" customHeight="true">
@@ -2127,16 +2133,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,98 +2151,98 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
       <c r="A17" s="97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2275,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2289,19 +2295,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,60 +2315,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
       <c r="A26" s="151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2384,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2397,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,40 +2413,40 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="14.0" customHeight="true">
+    <row r="32" ht="10.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
     <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2448,16 +2454,16 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.6</t>
+    <t>日期:2026.5.8</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-15</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>33-38</t>
+    <t>25-38</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,9 +68,6 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-15</t>
-  </si>
-  <si>
     <t>草鱼</t>
   </si>
   <si>
@@ -83,42 +80,39 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
+    <t>8.5-9.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
     <t>8.5-10</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-10</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -131,7 +125,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>38-47</t>
+    <t>37-47</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -143,7 +137,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-57</t>
+    <t>20-58</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -152,7 +146,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.8-7.3</t>
+    <t>6.7-7.2</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -206,25 +200,25 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>117</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-21-17</t>
+    <t>23-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>96</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58-40</t>
+    <t>74-61-45</t>
   </si>
   <si>
     <t>河虾(150头)</t>
@@ -236,13 +230,13 @@
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-36-30</t>
+    <t>42-35-29</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>77</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -251,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>60</t>
+    <t>64</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +263,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>23-29</t>
+    <t>21-25</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -287,7 +281,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>6-7</t>
   </si>
 </sst>
 </file>
@@ -1896,7 +1890,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +1900,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="12.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1994,93 +1988,93 @@
         <v>17</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D7" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="42" t="s">
         <v>19</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" ht="14.0" customHeight="true">
       <c r="A8" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="C8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="D8" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="47" t="s">
+      <c r="F8" s="48" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="D9" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="F9" s="54" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="59" t="s">
-        <v>33</v>
-      </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2113,19 +2107,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="10.0" customHeight="true">
@@ -2133,16 +2127,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2151,98 +2145,98 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
       <c r="A17" s="97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="99" t="s">
+      <c r="F17" s="102" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="100" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="101" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2275,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2295,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2315,60 +2309,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
       <c r="A26" s="151" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="154" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="155" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="154" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="155" t="s">
-        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="160" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="161" t="s">
-        <v>80</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2384,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2397,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="C30" s="177" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2413,40 +2407,40 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="10.0" customHeight="true">
+    <row r="32" ht="14.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
     <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,16 +2448,16 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.8</t>
+    <t>日期:2026.5.9</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -125,7 +125,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>37-47</t>
+    <t>37-46</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -200,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>117</t>
+    <t>115</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>23-20-17</t>
+    <t>24-21-18</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>96</t>
+    <t>94</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>74-61-45</t>
+    <t>74-62-45</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>85</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-35-29</t>
+    <t>43-37-29</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>77</t>
+    <t>75</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>64</t>
+    <t>62</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -263,7 +263,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>21-25</t>
+    <t>22-25</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -272,7 +272,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>8-11</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -281,7 +281,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>7-8</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1890,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="12.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2416,7 +2416,7 @@
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="14.0" customHeight="true">
+    <row r="32" ht="10.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.5.9</t>
+    <t>日期: 2026.5.10</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>25-38</t>
+    <t>26-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -80,15 +80,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>9-9.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-9.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-10</t>
+    <t>9-10</t>
   </si>
   <si>
     <t>7</t>
@@ -119,7 +122,7 @@
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂货类批发价格:</t>
+    <t>杂 货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
@@ -146,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.7-7.2</t>
+    <t>6.9-7.4</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -161,13 +164,13 @@
     <t>10-14</t>
   </si>
   <si>
-    <t>蛳螺(养殖)</t>
+    <t>蛳 螺(养殖)</t>
   </si>
   <si>
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鮰鱼</t>
+    <t>鲴鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -179,7 +182,7 @@
     <t>8.5-12</t>
   </si>
   <si>
-    <t>昂刺鱼</t>
+    <t>昂 刺鱼</t>
   </si>
   <si>
     <t>10-13</t>
@@ -200,7 +203,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>115</t>
+    <t>120</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -212,19 +215,19 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>94</t>
+    <t>99</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>74-62-45</t>
+    <t>75-64-46</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>85</t>
+    <t>89</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
@@ -236,7 +239,7 @@
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>78</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>62</t>
+    <t>67</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -263,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>22-25</t>
+    <t>18-21</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -272,16 +275,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>10-12</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
-  </si>
-  <si>
-    <t>7-8</t>
   </si>
 </sst>
 </file>
@@ -1882,7 +1882,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -1960,7 +1960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="10.0" customHeight="true">
+    <row r="6" ht="14.0" customHeight="true">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2022,59 +2022,59 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>22</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" ht="10.0" customHeight="true">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="10.0" customHeight="true">
+    <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,36 +2107,36 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="10.0" customHeight="true">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" ht="14.0" customHeight="true">
       <c r="A15" s="85" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,19 +2145,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2165,78 +2165,78 @@
         <v>20</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" ht="14.0" customHeight="true">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,39 +2269,39 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" ht="14.0" customHeight="true">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="10.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,60 +2309,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" ht="10.0" customHeight="true">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="14.0" customHeight="true">
       <c r="A26" s="151" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="10.0" customHeight="true">
+    <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,57 +2407,57 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="10.0" customHeight="true">
+    <row r="32" ht="14.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="14.0" customHeight="true">
+    <row r="33" ht="10.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>20</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
       <c r="F33" s="198"/>
     </row>
-    <row r="34" ht="11.0" customHeight="true">
+    <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2475,7 +2475,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.10</t>
+    <t>日期: 2026.5.11</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -71,7 +71,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>9.5-11.5</t>
   </si>
   <si>
     <t>4</t>
@@ -86,7 +86,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>9-9.5</t>
+    <t>9-10</t>
   </si>
   <si>
     <t>5</t>
@@ -113,9 +113,6 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9-10</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -128,7 +125,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>37-46</t>
+    <t>36-47</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +137,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-58</t>
+    <t>20-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -155,7 +152,7 @@
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>30-57</t>
+    <t>29-40</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>120</t>
+    <t>112</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>24-21-18</t>
+    <t>22-21-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>99</t>
+    <t>93</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>75-64-46</t>
+    <t>72-65-48</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>89</t>
+    <t>78</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>43-37-29</t>
+    <t>43-37-31</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>69</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>67</t>
+    <t>56</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -275,13 +272,16 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-12</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -2055,26 +2055,26 @@
         <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2107,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2127,16 +2127,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,19 +2145,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2165,19 +2165,19 @@
         <v>20</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2185,14 +2185,14 @@
         <v>25</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>30</v>
@@ -2203,40 +2203,40 @@
         <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2289,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,19 +2309,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2329,16 +2329,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2347,22 +2347,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,10 +2407,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2421,13 +2421,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>86</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2437,10 +2437,10 @@
         <v>20</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2451,13 +2451,13 @@
         <v>25</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>89</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>29</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.11</t>
+    <t>日期: 2026.5.12</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,30 +44,33 @@
     <t>鲫鱼</t>
   </si>
   <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>鳜鱼(桂鱼)</t>
+  </si>
+  <si>
+    <t>26-37</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>4-4.5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
     <t>10-15</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>鳜鱼(桂鱼)</t>
-  </si>
-  <si>
-    <t>26-37</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>4-4.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
     <t>草鱼</t>
   </si>
   <si>
@@ -86,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>9-10</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>5</t>
@@ -113,6 +116,9 @@
     <t>青鱼</t>
   </si>
   <si>
+    <t>9-10.5</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -158,9 +164,6 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>10-14</t>
-  </si>
-  <si>
     <t>蛳 螺(养殖)</t>
   </si>
   <si>
@@ -200,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>112</t>
+    <t>130</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-21-17</t>
+    <t>22-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>108</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-65-48</t>
+    <t>73-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>84</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>43-37-31</t>
+    <t>45-37-31</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>69</t>
+    <t>73</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>56</t>
+    <t>55</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -263,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-21</t>
+    <t>18-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -272,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>8-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -1988,93 +1991,93 @@
         <v>17</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D7" s="40" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="14.0" customHeight="true">
       <c r="A8" s="43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2110,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2127,16 +2130,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,98 +2148,98 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
       <c r="A17" s="97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D17" s="100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2272,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2289,19 +2292,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,60 +2312,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
       <c r="A26" s="151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2421,26 +2424,26 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
     <row r="33" ht="10.0" customHeight="true">
       <c r="A33" s="193" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2448,16 +2451,16 @@
     </row>
     <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.12</t>
+    <t>日期: 2026.5.13</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,126 +44,126 @@
     <t>鲫鱼</t>
   </si>
   <si>
+    <t>8-14</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>鳜鱼(桂鱼)</t>
+  </si>
+  <si>
+    <t>28-37</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>3.5-4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂 货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>36-45</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-54</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>6.8-7.4</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
     <t>10-14</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>鳜鱼(桂鱼)</t>
-  </si>
-  <si>
-    <t>26-37</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>4-4.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-15</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>9.5-11.5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>9.5-10.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-10.5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂 货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>36-47</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>6.9-7.4</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-40</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
     <t>蛳 螺(养殖)</t>
   </si>
   <si>
@@ -185,9 +185,6 @@
     <t>昂 刺鱼</t>
   </si>
   <si>
-    <t>10-13</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -203,37 +200,37 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>130</t>
+    <t>118</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-17</t>
+    <t>20-19-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>102</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-58</t>
+    <t>72-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>84</t>
+    <t>85</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>45-37-31</t>
+    <t>40-35-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -266,7 +263,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-20</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +272,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>8-11</t>
+    <t>8-10</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +281,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>6-7</t>
   </si>
 </sst>
 </file>
@@ -2020,64 +2017,64 @@
         <v>24</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2110,19 +2107,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2130,16 +2127,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2148,19 +2145,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2168,10 +2165,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>10</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
@@ -2185,25 +2182,25 @@
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="107" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>54</v>
@@ -2212,34 +2209,34 @@
         <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
         <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2292,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2309,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2332,40 +2329,40 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="159" t="s">
+      <c r="D27" s="160" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>78</v>
-      </c>
-      <c r="D27" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="161" t="s">
-        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,10 +2407,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,13 +2421,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>86</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2437,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2451,16 +2448,16 @@
     </row>
     <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>89</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.13</t>
+    <t>日期: 2026.5.14</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>28-37</t>
+    <t>27-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -89,6 +89,9 @@
     <t>花鲢</t>
   </si>
   <si>
+    <t>9.5-10.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -113,7 +116,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>9.5-10</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>36-45</t>
+    <t>26-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-54</t>
+    <t>20-43</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>6.8-7.4</t>
+    <t>7-7.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -200,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-19-17</t>
+    <t>21-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>87</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -224,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>85</t>
+    <t>75</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-35-27</t>
+    <t>41-36-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>73</t>
+    <t>68</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>55</t>
+    <t>52</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -263,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>15-18</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -281,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>5-7</t>
   </si>
 </sst>
 </file>
@@ -2017,64 +2020,64 @@
         <v>24</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2110,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2127,16 +2130,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2165,54 +2168,54 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
         <v>18</v>
@@ -2220,23 +2223,23 @@
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2272,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2289,19 +2292,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,19 +2312,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2329,40 +2332,40 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2421,13 +2424,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2437,10 +2440,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2448,16 +2451,16 @@
     </row>
     <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.14</t>
+    <t>日期: 2026.5.15</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>27-37</t>
+    <t>27-36</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -116,22 +116,19 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-10</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂 货类批发价格:</t>
+    <t>杂货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>26-45</t>
+    <t>34-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -152,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7-7.5</t>
+    <t>7-7.4</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -173,7 +170,7 @@
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鲴鱼</t>
+    <t>鯝鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -203,37 +200,37 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>110</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>21-20-17</t>
+    <t>22-20-18</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>89</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-58</t>
+    <t>74-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>76</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>41-36-30</t>
+    <t>42-37-31</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +263,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>15-18</t>
+    <t>16-19</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +272,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +281,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>5-7</t>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1882,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2058,26 +2055,26 @@
         <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2110,19 +2107,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2130,16 +2127,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2148,19 +2145,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2168,19 +2165,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2188,14 +2185,14 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
@@ -2206,16 +2203,16 @@
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
         <v>18</v>
@@ -2223,23 +2220,23 @@
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2292,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2309,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2332,16 +2329,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2350,22 +2347,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,26 +2391,26 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,13 +2421,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>86</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2437,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2451,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>89</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2478,7 +2475,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.15</t>
+    <t>日期: 2026.5.16</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -89,33 +89,36 @@
     <t>花鲢</t>
   </si>
   <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
     <t>9.5-10.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -128,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>34-45</t>
+    <t>35-46</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-43</t>
+    <t>20-42</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -170,7 +173,7 @@
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鯝鱼</t>
+    <t>鲴鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -200,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>110</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-18</t>
+    <t>21-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>89</t>
+    <t>90</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>74-60</t>
+    <t>73-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>77</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-37-31</t>
+    <t>42-37-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>64</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>53</t>
+    <t>50</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -2040,7 +2043,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>31</v>
       </c>
@@ -2055,26 +2058,26 @@
         <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="14.0" customHeight="true">
+    <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2110,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2127,16 +2130,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2165,19 +2168,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2185,34 +2188,34 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" ht="10.0" customHeight="true">
+    <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
         <v>18</v>
@@ -2220,23 +2223,23 @@
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2272,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2289,19 +2292,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,19 +2312,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2329,16 +2332,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2347,22 +2350,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,26 +2394,26 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2421,26 +2424,26 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="10.0" customHeight="true">
+    <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2451,13 +2454,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.16</t>
+    <t>日期: 2026.5.17</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -125,13 +125,13 @@
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂货类批发价格:</t>
+    <t>杂 货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-46</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -152,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7-7.4</t>
+    <t>7-7.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -164,7 +164,7 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>蛳 螺(养殖)</t>
@@ -173,7 +173,7 @@
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鲴鱼</t>
+    <t>鯝鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>118</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>21-20-17</t>
+    <t>22-21-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>98</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-58</t>
+    <t>74-64</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>77</t>
+    <t>84</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-37-28</t>
+    <t>42-35-29</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>64</t>
+    <t>72</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>50</t>
+    <t>53</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>16-19</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -1885,7 +1885,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2043,7 +2043,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>31</v>
       </c>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="10.0" customHeight="true">
+    <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
         <v>37</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" ht="14.0" customHeight="true">
+    <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
         <v>31</v>
       </c>
@@ -2435,7 +2435,7 @@
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="14.0" customHeight="true">
+    <row r="33" ht="10.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
@@ -2478,7 +2478,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.17</t>
+    <t>日期: 2026.5.19</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>27-36</t>
+    <t>28-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -131,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-45</t>
+    <t>37-48</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -143,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-42</t>
+    <t>20-43</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -152,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7-7.5</t>
+    <t>7.3-7.8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -164,16 +164,16 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>9.5-13</t>
   </si>
   <si>
     <t>蛳 螺(养殖)</t>
   </si>
   <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鯝鱼</t>
+    <t>3-3.5</t>
+  </si>
+  <si>
+    <t>鲴鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -188,6 +188,9 @@
     <t>昂 刺鱼</t>
   </si>
   <si>
+    <t>10-13</t>
+  </si>
+  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -203,43 +206,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>123</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-21-16</t>
+    <t>22-21-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>98</t>
+    <t>102</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>74-64</t>
+    <t>75-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>84</t>
+    <t>85</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-35-29</t>
+    <t>42-35-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>72</t>
+    <t>70</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +251,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>53</t>
+    <t>56</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>17-19</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +278,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>8-10</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +287,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>6-7</t>
   </si>
 </sst>
 </file>
@@ -2218,7 +2221,7 @@
         <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2226,20 +2229,20 @@
         <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2275,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2292,19 +2295,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2315,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2332,16 +2335,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2350,22 +2353,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2384,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2397,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,13 +2427,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2443,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2457,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.19</t>
+    <t>日期: 2026.5.20</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>28-37</t>
+    <t>27-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -116,9 +116,6 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -152,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.3-7.8</t>
+    <t>7.3-7.9</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -170,7 +167,7 @@
     <t>蛳 螺(养殖)</t>
   </si>
   <si>
-    <t>3-3.5</t>
+    <t>3-5.5</t>
   </si>
   <si>
     <t>鲴鱼</t>
@@ -206,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>123</t>
+    <t>120</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-21-17</t>
+    <t>20-18-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>100</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -230,7 +227,7 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>85</t>
+    <t>82</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
@@ -242,7 +239,7 @@
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>68</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -251,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>56</t>
+    <t>54</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-19</t>
+    <t>16-19</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -287,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>5-7</t>
   </si>
 </sst>
 </file>
@@ -2061,26 +2058,26 @@
         <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2113,19 +2110,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2133,16 +2130,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2151,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2171,19 +2168,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2191,14 +2188,14 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
@@ -2209,40 +2206,40 @@
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2275,19 +2272,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>65</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2295,19 +2292,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>67</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>69</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2315,19 +2312,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>73</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2335,16 +2332,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2353,22 +2350,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2384,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2397,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2413,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2427,13 +2424,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>87</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2443,10 +2440,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2457,13 +2454,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>90</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.20</t>
+    <t>日期: 2026.5.21</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-10</t>
   </si>
   <si>
     <t>5</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>37-48</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-43</t>
+    <t>20-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.3-7.9</t>
+    <t>7.5-8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>120</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-14</t>
+    <t>22-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>100</t>
+    <t>92</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>75-60</t>
+    <t>72-60-50</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>82</t>
+    <t>78</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-35-28</t>
+    <t>41-36-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>69</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>54</t>
+    <t>52</t>
   </si>
   <si>
     <t>黑虎虾</t>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.21</t>
+    <t>日期: 2026.5.23</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>27-37</t>
+    <t>27-35</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>10-13</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8.5-10</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>5</t>
@@ -122,7 +122,7 @@
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂 货类批发价格:</t>
+    <t>杂货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.5-8</t>
+    <t>7.7-8.3</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,9 +185,6 @@
     <t>昂 刺鱼</t>
   </si>
   <si>
-    <t>10-13</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>113</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>22-20-17</t>
+    <t>21-20-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>92</t>
+    <t>93</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-60-50</t>
+    <t>72-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>75</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>41-36-30</t>
+    <t>41-35-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>69</t>
+    <t>68</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -266,7 +263,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>16-19</t>
+    <t>18-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +272,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +281,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>5-7</t>
+    <t>7-8</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1882,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2043,7 +2040,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>31</v>
       </c>
@@ -2075,7 +2072,7 @@
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="14.0" customHeight="true">
+    <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
         <v>36</v>
       </c>
@@ -2201,7 +2198,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" ht="10.0" customHeight="true">
+    <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
         <v>31</v>
       </c>
@@ -2218,7 +2215,7 @@
         <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2226,20 +2223,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2292,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2309,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2332,16 +2329,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2350,22 +2347,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,10 +2407,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,26 +2421,26 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>86</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="10.0" customHeight="true">
+    <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2451,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>89</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2478,7 +2475,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.23</t>
+    <t>日期: 2026.5.24</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>27-35</t>
+    <t>26-36</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,123 +68,129 @@
     <t>鲈鱼</t>
   </si>
   <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>9.5-10.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9-10.5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂 货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-47</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-56</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>7.3-7.8</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>9.5-13</t>
+  </si>
+  <si>
+    <t>蛳 螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鲴鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
+    <t>8.5-12</t>
+  </si>
+  <si>
+    <t>昂 刺鱼</t>
+  </si>
+  <si>
     <t>10-13</t>
   </si>
   <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>9.5-10.5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-10.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-45</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>7.7-8.3</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>9.5-13</t>
-  </si>
-  <si>
-    <t>蛳 螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鲴鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
-    <t>8.5-12</t>
-  </si>
-  <si>
-    <t>昂 刺鱼</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -200,43 +206,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>113</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>21-20-17</t>
+    <t>20-19-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>90</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-60</t>
+    <t>70-60-47</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>78</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>41-35-28</t>
+    <t>42-38-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>65</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +251,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>52</t>
+    <t>48</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -263,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-22</t>
+    <t>16-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -272,7 +278,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>8-10</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -281,7 +287,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>7-8</t>
+    <t>5-7</t>
   </si>
 </sst>
 </file>
@@ -1882,7 +1888,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2040,7 +2046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>31</v>
       </c>
@@ -2055,26 +2061,26 @@
         <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="10.0" customHeight="true">
+    <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2113,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2127,16 +2133,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,19 +2151,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2165,19 +2171,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2185,58 +2191,58 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" ht="14.0" customHeight="true">
+    <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2275,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2289,19 +2295,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,19 +2315,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2329,16 +2335,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2347,22 +2353,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2384,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2397,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2421,26 +2427,26 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="14.0" customHeight="true">
+    <row r="33" ht="10.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2451,13 +2457,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2475,7 +2481,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.24</t>
+    <t>日期: 2026.5.26</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>8-12</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>26-36</t>
+    <t>27-35</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,51 +74,51 @@
     <t>草鱼</t>
   </si>
   <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
     <t>9.5-10.5</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-10.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-10.5</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -131,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-47</t>
+    <t>36-48</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -152,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.3-7.8</t>
+    <t>7.4-7.8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -164,7 +164,7 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>9.5-13</t>
+    <t>9.5-12.5</t>
   </si>
   <si>
     <t>蛳 螺(养殖)</t>
@@ -212,7 +212,7 @@
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-19-16</t>
+    <t>20-19-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
@@ -224,7 +224,7 @@
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-60-47</t>
+    <t>72-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
@@ -236,13 +236,13 @@
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>42-38-30</t>
+    <t>40-35-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>65</t>
+    <t>70</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -251,7 +251,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>48</t>
+    <t>53</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>16-20</t>
+    <t>16-19</t>
   </si>
   <si>
     <t>7-9红</t>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.26</t>
+    <t>日期: 2026.5.28</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -131,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>36-48</t>
+    <t>36-53</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -143,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-56</t>
+    <t>20-55</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -152,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.4-7.8</t>
+    <t>8-8.6</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -173,7 +173,7 @@
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鲴鱼</t>
+    <t>鯝鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -182,13 +182,10 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>8.5-12</t>
-  </si>
-  <si>
     <t>昂 刺鱼</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>10-12</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -206,13 +203,13 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>113</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-19-17</t>
+    <t>19-18-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
@@ -224,7 +221,7 @@
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-58</t>
+    <t>70-62</t>
   </si>
   <si>
     <t>河虾(150头)</t>
@@ -236,13 +233,13 @@
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-35-27</t>
+    <t>40-35-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>69</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -251,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>53</t>
+    <t>56</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>16-19</t>
+    <t>15-18</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -278,16 +275,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>7-9</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
-  </si>
-  <si>
-    <t>5-7</t>
   </si>
 </sst>
 </file>
@@ -2212,16 +2206,16 @@
         <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2229,20 +2223,20 @@
         <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2275,19 +2269,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>65</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2295,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>67</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>69</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2315,19 +2309,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>73</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2335,16 +2329,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2353,22 +2347,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2384,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2397,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2413,10 +2407,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2427,13 +2421,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>87</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2443,10 +2437,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2457,13 +2451,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.28</t>
+    <t>日期: 2026.5.30</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-12</t>
+    <t>10-13</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>27-35</t>
+    <t>27-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -83,7 +83,7 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
@@ -92,9 +92,6 @@
     <t>8.5-10.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -116,22 +113,19 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂 货类批发价格:</t>
+    <t>杂货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>36-53</t>
+    <t>36-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -143,7 +137,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-55</t>
+    <t>20-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -152,7 +146,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>8-8.6</t>
+    <t>9.2-9.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -164,7 +158,7 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>9.5-12.5</t>
+    <t>9.5-12</t>
   </si>
   <si>
     <t>蛳 螺(养殖)</t>
@@ -173,7 +167,7 @@
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鯝鱼</t>
+    <t>鲴鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -182,12 +176,12 @@
     <t>黑鱼</t>
   </si>
   <si>
+    <t>8.5-12</t>
+  </si>
+  <si>
     <t>昂 刺鱼</t>
   </si>
   <si>
-    <t>10-12</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -203,43 +197,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>113</t>
+    <t>105</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>19-18-16</t>
+    <t>20-18-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>89</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-62</t>
+    <t>70-56</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>76</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-35-26</t>
+    <t>37-33-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>69</t>
+    <t>70</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +242,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>56</t>
+    <t>55</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +260,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>15-18</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,13 +269,16 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -1882,7 +1879,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2022,59 +2019,59 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="54" t="s">
+    </row>
+    <row r="10" ht="10.0" customHeight="true">
+      <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" ht="14.0" customHeight="true">
-      <c r="A10" s="55" t="s">
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="66"/>
+    </row>
+    <row r="12" ht="10.0" customHeight="true">
+      <c r="A12" s="67" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="66"/>
-    </row>
-    <row r="12" ht="14.0" customHeight="true">
-      <c r="A12" s="67" t="s">
-        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2107,19 +2104,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2127,16 +2124,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2145,19 +2142,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2165,78 +2162,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="108" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="14.0" customHeight="true">
+      <c r="A19" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="108" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" ht="10.0" customHeight="true">
-      <c r="A19" s="109" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="110" t="s">
+      <c r="D19" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="111" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
-        <v>56</v>
-      </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2269,19 +2266,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2289,19 +2286,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2309,19 +2306,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2329,40 +2326,40 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="159" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="161" t="s">
-        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2378,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2391,13 +2388,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="177" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="178" t="s">
         <v>82</v>
-      </c>
-      <c r="C30" s="177" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2407,10 +2404,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2421,26 +2418,26 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="10.0" customHeight="true">
+    <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2448,16 +2445,16 @@
     </row>
     <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2475,7 +2472,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.5.30</t>
+    <t>日期:2026.6.1</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>8-13</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>27-37</t>
+    <t>33-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -83,15 +83,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-10.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -113,6 +116,9 @@
     <t>青鱼</t>
   </si>
   <si>
+    <t>9.5-10.5</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -125,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>36-52</t>
+    <t>35-53</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -137,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-56</t>
+    <t>20-55</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -146,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.2-9.7</t>
+    <t>10-10.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -161,13 +167,13 @@
     <t>9.5-12</t>
   </si>
   <si>
-    <t>蛳 螺(养殖)</t>
+    <t>蛳螺(养殖)</t>
   </si>
   <si>
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鲴鱼</t>
+    <t>鮰鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -179,7 +185,7 @@
     <t>8.5-12</t>
   </si>
   <si>
-    <t>昂 刺鱼</t>
+    <t>昂刺鱼</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -197,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-14</t>
+    <t>20-19-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>89</t>
+    <t>96</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -221,13 +227,13 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>79</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-33-28</t>
+    <t>40-35-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -242,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>55</t>
+    <t>52</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -260,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>15-19</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -1887,7 +1893,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1903,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="12.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1957,7 +1963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="14.0" customHeight="true">
+    <row r="6" ht="10.0" customHeight="true">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2019,59 +2025,59 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2104,36 +2110,36 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="14.0" customHeight="true">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="10.0" customHeight="true">
       <c r="A15" s="85" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2142,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2162,78 +2168,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2266,39 +2272,39 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" ht="10.0" customHeight="true">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="14.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2306,60 +2312,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" ht="14.0" customHeight="true">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="10.0" customHeight="true">
       <c r="A26" s="151" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="14.0" customHeight="true">
+    <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2375,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2388,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2404,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2418,13 +2424,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2434,27 +2440,27 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
       <c r="F33" s="198"/>
     </row>
-    <row r="34" ht="10.0" customHeight="true">
+    <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.1</t>
+    <t>日期:2026.6.3</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3.5-4</t>
+    <t>3-4</t>
   </si>
   <si>
     <t>3</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-9.5</t>
   </si>
   <si>
     <t>5</t>
@@ -116,7 +116,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
+    <t>9.5-10</t>
   </si>
   <si>
     <t>7</t>
@@ -131,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-53</t>
+    <t>35-54</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -152,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10-10.5</t>
+    <t>10.4-10.8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -188,6 +188,9 @@
     <t>昂刺鱼</t>
   </si>
   <si>
+    <t>10-15</t>
+  </si>
+  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -215,31 +218,31 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>96</t>
+    <t>90</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-56</t>
+    <t>70-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>79</t>
+    <t>76</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-35-30</t>
+    <t>40-37-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>67</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -266,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>15-19</t>
+    <t>14-17</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +278,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>8-10</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +287,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>5-7</t>
   </si>
 </sst>
 </file>
@@ -2218,7 +2221,7 @@
         <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2226,20 +2229,20 @@
         <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,19 +2275,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2292,19 +2295,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,19 +2315,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2332,16 +2335,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2350,22 +2353,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2384,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2397,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2424,13 +2427,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2443,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2457,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.3</t>
+    <t>日期: 2026.6.5</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,157 +44,154 @@
     <t>鲫鱼</t>
   </si>
   <si>
+    <t>8-12</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>鳜鱼(桂鱼)</t>
+  </si>
+  <si>
+    <t>33-35</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>8-14.5</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>9.5-10.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-9.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂 货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-54</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-56</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>10.6-11</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>9.5-12</t>
+  </si>
+  <si>
+    <t>蛳 螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鲴鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
+    <t>昂 刺鱼</t>
+  </si>
+  <si>
     <t>8-13</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>鳜鱼(桂鱼)</t>
-  </si>
-  <si>
-    <t>33-37</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-14</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>9.5-10.5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-9.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9.5-10</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-54</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-55</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>10.4-10.8</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>9.5-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
-    <t>8.5-12</t>
-  </si>
-  <si>
-    <t>昂刺鱼</t>
-  </si>
-  <si>
-    <t>10-15</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
-    <t>12.5</t>
+    <t>13.5</t>
   </si>
   <si>
     <t>梭子蟹(大中小)</t>
@@ -206,37 +203,37 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>103</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-19-16</t>
+    <t>20-18-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>89</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58</t>
+    <t>73-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>74</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-37-30</t>
+    <t>43-39-32</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -251,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>52</t>
+    <t>55</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>14-17</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -278,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>11-14</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -287,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>5-7</t>
+    <t>7-9</t>
   </si>
 </sst>
 </file>
@@ -1888,7 +1885,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -1896,7 +1893,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +1903,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="12.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1966,7 +1963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="10.0" customHeight="true">
+    <row r="6" ht="14.0" customHeight="true">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2046,7 +2043,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>31</v>
       </c>
@@ -2061,26 +2058,26 @@
         <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="F11" s="66"/>
+    </row>
+    <row r="12" ht="14.0" customHeight="true">
+      <c r="A12" s="67" t="s">
         <v>36</v>
-      </c>
-      <c r="F11" s="66"/>
-    </row>
-    <row r="12" ht="10.0" customHeight="true">
-      <c r="A12" s="67" t="s">
-        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2113,36 +2110,36 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="84" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" ht="10.0" customHeight="true">
+    </row>
+    <row r="15" ht="14.0" customHeight="true">
       <c r="A15" s="85" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2151,19 +2148,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2171,19 +2168,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2191,58 +2188,58 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" ht="14.0" customHeight="true">
+    <row r="19" ht="10.0" customHeight="true">
       <c r="A19" s="109" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2275,39 +2272,39 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="138" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" ht="14.0" customHeight="true">
+    </row>
+    <row r="24" ht="10.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>67</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>69</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2315,60 +2312,60 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="150" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" ht="10.0" customHeight="true">
+    </row>
+    <row r="26" ht="14.0" customHeight="true">
       <c r="A26" s="151" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="10.0" customHeight="true">
+    <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2384,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2397,13 +2394,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2413,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2427,43 +2424,43 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>87</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="14.0" customHeight="true">
+    <row r="33" ht="10.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
       <c r="F33" s="198"/>
     </row>
-    <row r="34" ht="11.0" customHeight="true">
+    <row r="34" ht="10.0" customHeight="true">
       <c r="A34" s="199" t="s">
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>90</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2481,7 +2478,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期: 2026.6.5</t>
+    <t>日期:2026.6.6</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8.5-9.5</t>
+    <t>7.5-9.5</t>
   </si>
   <si>
     <t>5</t>
@@ -122,13 +122,13 @@
     <t>鲳鱼</t>
   </si>
   <si>
-    <t>杂 货类批发价格:</t>
+    <t>杂货类批发价格:</t>
   </si>
   <si>
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-54</t>
+    <t>35-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-56</t>
+    <t>20-55</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10.6-11</t>
+    <t>10.7-11.2</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -161,16 +161,13 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>9.5-12</t>
-  </si>
-  <si>
-    <t>蛳 螺(养殖)</t>
+    <t>蛳螺(养殖)</t>
   </si>
   <si>
     <t>3-5.5</t>
   </si>
   <si>
-    <t>鲴鱼</t>
+    <t>鮰鱼</t>
   </si>
   <si>
     <t>鲶鱼</t>
@@ -179,13 +176,13 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
-    <t>昂 刺鱼</t>
-  </si>
-  <si>
-    <t>8-13</t>
+    <t>7.5-9</t>
+  </si>
+  <si>
+    <t>昂刺鱼</t>
+  </si>
+  <si>
+    <t>10-13</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>103</t>
+    <t>100</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-16</t>
+    <t>20-18-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>89</t>
+    <t>87</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-60</t>
+    <t>73-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>74</t>
+    <t>72</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>43-39-32</t>
+    <t>41-37-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>67</t>
+    <t>68</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,10 +245,13 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>55</t>
+    <t>53</t>
   </si>
   <si>
     <t>黑虎虾</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t>龙虾类批发价格:</t>
@@ -1557,37 +1557,40 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1599,139 +1602,139 @@
     <xf numFmtId="0" fontId="86" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1743,11 +1746,8 @@
     <xf numFmtId="0" fontId="126" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -1885,7 +1885,7 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -1963,7 +1963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="14.0" customHeight="true">
+    <row r="6" ht="10.0" customHeight="true">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>31</v>
       </c>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F11" s="66"/>
     </row>
-    <row r="12" ht="14.0" customHeight="true">
+    <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
         <v>36</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="14.0" customHeight="true">
+    <row r="15" ht="10.0" customHeight="true">
       <c r="A15" s="85" t="s">
         <v>11</v>
       </c>
@@ -2170,17 +2170,15 @@
       <c r="B17" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="99" t="s">
-        <v>49</v>
-      </c>
+      <c r="C17" s="99"/>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2188,37 +2186,37 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" ht="10.0" customHeight="true">
+    <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2226,20 +2224,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2272,39 +2270,39 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" ht="10.0" customHeight="true">
+    </row>
+    <row r="24" ht="14.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2312,56 +2310,58 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" ht="14.0" customHeight="true">
+    </row>
+    <row r="26" ht="10.0" customHeight="true">
       <c r="A26" s="151" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="14.0" customHeight="true">
+    <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
@@ -2419,7 +2419,7 @@
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="14.0" customHeight="true">
+    <row r="32" ht="10.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
@@ -2435,7 +2435,7 @@
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
-    <row r="33" ht="10.0" customHeight="true">
+    <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
         <v>21</v>
       </c>
@@ -2449,7 +2449,7 @@
       <c r="E33" s="197"/>
       <c r="F33" s="198"/>
     </row>
-    <row r="34" ht="10.0" customHeight="true">
+    <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
         <v>26</v>
       </c>
@@ -2478,7 +2478,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="D29:F29"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.6</t>
+    <t>日期:2026.6.10</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>33-35</t>
+    <t>33-37</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-9.5</t>
+    <t>7.5-9</t>
   </si>
   <si>
     <t>5</t>
@@ -116,6 +116,9 @@
     <t>青鱼</t>
   </si>
   <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -128,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-52</t>
+    <t>35-54</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +143,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-55</t>
+    <t>21-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +152,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10.7-11.2</t>
+    <t>11-11.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -161,6 +164,9 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
+    <t>9.5-12</t>
+  </si>
+  <si>
     <t>蛳螺(养殖)</t>
   </si>
   <si>
@@ -176,13 +182,10 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -200,25 +203,25 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>100</t>
+    <t>105</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-17</t>
+    <t>20-19-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>90</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-58</t>
+    <t>73-56</t>
   </si>
   <si>
     <t>河虾(150头)</t>
@@ -236,7 +239,7 @@
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>63</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>53</t>
+    <t>48</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>16-19</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +278,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>11-14</t>
+    <t>10-12</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -292,13 +295,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="151">
+  <fonts count="152">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1557,40 +1565,37 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1602,28 +1607,31 @@
     <xf numFmtId="0" fontId="86" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -1641,10 +1649,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1656,13 +1661,13 @@
     <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1674,13 +1679,13 @@
     <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1692,13 +1697,13 @@
     <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1710,13 +1715,13 @@
     <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1728,13 +1733,13 @@
     <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1746,10 +1751,13 @@
     <xf numFmtId="0" fontId="126" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -1767,10 +1775,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1779,16 +1784,16 @@
     <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1797,21 +1802,24 @@
     <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1821,10 +1829,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
@@ -1833,21 +1838,24 @@
     <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,16 +1865,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="150" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
@@ -1893,7 +1901,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1903,7 +1911,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="12.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2058,26 +2066,26 @@
         <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2105,24 +2113,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="14.0" customHeight="true">
+    <row r="14" ht="10.0" customHeight="true">
       <c r="A14" s="79" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="10.0" customHeight="true">
@@ -2130,16 +2138,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2148,19 +2156,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2168,17 +2176,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="99"/>
+        <v>49</v>
+      </c>
+      <c r="C17" s="99" t="s">
+        <v>50</v>
+      </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2186,14 +2196,14 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>31</v>
@@ -2204,40 +2214,40 @@
         <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2270,19 +2280,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2290,19 +2300,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2310,19 +2320,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2330,16 +2340,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2348,24 +2358,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2381,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2394,13 +2404,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2410,27 +2420,27 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="10.0" customHeight="true">
+    <row r="32" ht="14.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2440,10 +2450,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2454,13 +2464,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.10</t>
+    <t>日期:2026.6.11</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>33-37</t>
+    <t>35-40</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>8-14.5</t>
+    <t>8-15</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -83,109 +83,106 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-50</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-55</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>11-11.5</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>9.5-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
     <t>7.5-9</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>8.5-10.5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-54</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>21-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>11-11.5</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>9.5-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>103</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-19-16</t>
+    <t>20-18-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>88</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-56</t>
+    <t>73-52</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>72</t>
+    <t>74</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>41-37-30</t>
+    <t>38-35-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>63</t>
+    <t>60</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>48</t>
+    <t>44</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>16-19</t>
+    <t>15-18</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -278,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-12</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -287,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -2033,59 +2030,59 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2118,19 +2115,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="10.0" customHeight="true">
@@ -2138,16 +2135,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2156,19 +2153,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2176,78 +2173,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="111" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2280,19 +2277,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2300,19 +2297,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2320,19 +2317,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2340,42 +2337,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="159" t="s">
+      <c r="D27" s="160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="161" t="s">
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2391,7 +2388,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2404,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2420,10 +2417,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2434,13 +2431,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>87</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2450,10 +2447,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2461,16 +2458,16 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>90</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.11</t>
+    <t>日期:2026.6.16</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-12</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-40</t>
+    <t>35-43</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>8-15</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -83,15 +83,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -104,9 +107,6 @@
     <t>8-9</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>红鱼</t>
   </si>
   <si>
@@ -146,7 +146,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>11-11.5</t>
+    <t>10.8-11.3</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -200,37 +200,37 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>103</t>
+    <t>95</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-15</t>
+    <t>18-16-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>88</t>
+    <t>80</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-52</t>
+    <t>65-52</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>74</t>
+    <t>67</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>38-35-30</t>
+    <t>36-30-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -245,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>44</t>
+    <t>47</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>15-18</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>10-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>7-9</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +1908,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="12.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="10.0" customHeight="true">
+    <row r="6" ht="14.0" customHeight="true">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2030,34 +2030,34 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>32</v>
@@ -2110,7 +2110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="10.0" customHeight="true">
+    <row r="14" ht="14.0" customHeight="true">
       <c r="A14" s="79" t="s">
         <v>6</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" ht="10.0" customHeight="true">
+    <row r="15" ht="14.0" customHeight="true">
       <c r="A15" s="85" t="s">
         <v>11</v>
       </c>
@@ -2190,25 +2190,25 @@
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>53</v>
@@ -2217,7 +2217,7 @@
         <v>54</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E19" s="113" t="s">
         <v>55</v>
@@ -2350,9 +2350,9 @@
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="10.0" customHeight="true">
+    <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>76</v>
@@ -2361,7 +2361,7 @@
         <v>77</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>78</v>
@@ -2426,7 +2426,7 @@
       <c r="E31" s="185"/>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="14.0" customHeight="true">
+    <row r="32" ht="10.0" customHeight="true">
       <c r="A32" s="187" t="s">
         <v>16</v>
       </c>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
         <v>82</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.16</t>
+    <t>日期:2026.6.17</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>2</t>
@@ -68,13 +68,13 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>10-14.5</t>
   </si>
   <si>
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -83,30 +83,33 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-9.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
     <t>红鱼</t>
   </si>
   <si>
@@ -158,7 +161,7 @@
     <t>泥鳅(养殖)</t>
   </si>
   <si>
-    <t>9.5-12</t>
+    <t>10-12</t>
   </si>
   <si>
     <t>蛳螺(养殖)</t>
@@ -182,9 +185,6 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-14</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -200,19 +200,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>95</t>
+    <t>98</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-16-14</t>
+    <t>19-18-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>80</t>
+    <t>83</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -224,19 +224,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>67</t>
+    <t>70</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-30-28</t>
+    <t>40-36-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>60</t>
+    <t>64</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>47</t>
+    <t>50</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>18-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>11-14</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>8-11</t>
   </si>
 </sst>
 </file>
@@ -2050,17 +2050,17 @@
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
         <v>20</v>
@@ -2068,21 +2068,21 @@
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2115,19 +2115,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2135,16 +2135,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2153,19 +2153,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2173,19 +2173,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2193,42 +2193,42 @@
         <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
         <v>57</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.17</t>
+    <t>日期:2026.6.19</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-43</t>
+    <t>35-44</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -83,7 +83,7 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
@@ -92,9 +92,6 @@
     <t>7.5-9.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
     <t>青鱼</t>
   </si>
   <si>
+    <t>8.5-11</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-50</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10.8-11.3</t>
+    <t>10.5-11</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -179,12 +179,12 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
+    <t>8-14.5</t>
+  </si>
+  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -200,52 +200,52 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>98</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>19-18-15</t>
+    <t>20-19-17</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>83</t>
+    <t>90</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>65-52</t>
+    <t>65-56</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>罗氏虾(大中小)</t>
+  </si>
+  <si>
+    <t>35-30</t>
+  </si>
+  <si>
+    <t>河虾(160头)</t>
+  </si>
+  <si>
     <t>70</t>
   </si>
   <si>
-    <t>罗氏虾(大中小)</t>
-  </si>
-  <si>
-    <t>40-36-28</t>
-  </si>
-  <si>
-    <t>河虾(160头)</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
     <t>斑节虾</t>
   </si>
   <si>
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>50</t>
+    <t>58</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-20</t>
+    <t>19-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>11-14</t>
+    <t>11-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-11</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -1898,7 +1898,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1908,7 +1908,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2030,40 +2030,40 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
@@ -2190,40 +2190,40 @@
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>76</v>
@@ -2361,7 +2361,7 @@
         <v>77</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>78</v>
@@ -2380,7 +2380,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="14.0" customHeight="true">
+    <row r="29" ht="10.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
         <v>82</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.19</t>
+    <t>日期:2026.6.20</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-44</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,13 +68,13 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-14.5</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -83,108 +83,108 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-9</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-50</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-56</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>10.8-11.2</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
   </si>
   <si>
     <t>7.5-9.5</t>
   </si>
   <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>8.5-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-45</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-55</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>10.5-11</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>8-14.5</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -200,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>103</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-19-17</t>
+    <t>20-18-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>88</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>65-56</t>
+    <t>65-53</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>73</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>35-30</t>
+    <t>40-35-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>64</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,15 +245,12 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>58</t>
+    <t>50</t>
   </si>
   <si>
     <t>黑虎虾</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>龙虾类批发价格:</t>
   </si>
   <si>
@@ -266,7 +263,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>19-20</t>
+    <t>19-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +272,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>11-13</t>
+    <t>13-15</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +281,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>9-12</t>
   </si>
 </sst>
 </file>
@@ -292,18 +289,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="152">
+  <fonts count="151">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1751,20 +1743,38 @@
     <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1772,16 +1782,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -1790,17 +1800,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1808,17 +1818,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1826,17 +1836,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1844,34 +1854,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="150" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2030,34 +2022,34 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>32</v>
@@ -2190,40 +2182,40 @@
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2352,7 +2344,7 @@
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>76</v>
@@ -2361,18 +2353,16 @@
         <v>77</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="162" t="s">
-        <v>79</v>
-      </c>
+      <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2388,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2401,13 +2391,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>84</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2417,10 +2407,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2431,13 +2421,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>86</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>87</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2447,10 +2437,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2458,16 +2448,16 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>89</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -32,7 +32,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.22</t>
+    <t>日期:2026.6.23</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -68,7 +68,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-43</t>
+    <t>35-44</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -83,123 +83,123 @@
     <t>鲈鱼</t>
   </si>
   <si>
+    <t>10-14.5</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-9.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-45</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-55</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>10.9-11.4</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
+    <t>昂刺鱼</t>
+  </si>
+  <si>
     <t>10-14</t>
   </si>
   <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>9.5-10.5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-9.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9.5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-45</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>10.9-11.4</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
-    <t>昂刺鱼</t>
-  </si>
-  <si>
-    <t>10-14.5</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -215,43 +215,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>基围虾(大中小)</t>
+  </si>
+  <si>
+    <t>17-16-13</t>
+  </si>
+  <si>
+    <t>河虾(130头)</t>
+  </si>
+  <si>
     <t>93</t>
   </si>
   <si>
-    <t>基围虾(大中小)</t>
-  </si>
-  <si>
-    <t>18-17-15</t>
-  </si>
-  <si>
-    <t>河虾(130头)</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>63-50</t>
+    <t>65-52</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>71</t>
+    <t>78</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>35-31-26</t>
+    <t>38-35-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>62</t>
+    <t>67</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -260,7 +260,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>48</t>
+    <t>50</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -281,7 +281,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>16-19</t>
+    <t>16-18</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -290,7 +290,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>8-11</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -299,7 +299,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>5-7</t>
   </si>
 </sst>
 </file>
@@ -921,7 +921,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1786,40 +1786,40 @@
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:6">
       <c r="A9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10" customHeight="1" spans="1:6">
       <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:6">
@@ -1946,25 +1946,25 @@
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:6">
       <c r="A19" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>54</v>
@@ -1973,7 +1973,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>55</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="27" ht="14" customHeight="1" spans="1:6">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>76</v>
@@ -2117,7 +2117,7 @@
         <v>77</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>78</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="34" ht="11" customHeight="1" spans="1:6">
       <c r="A34" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>82</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.24</t>
+    <t>日期:2026.6.25</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-11</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-40</t>
+    <t>35-39</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9-10.5</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -83,106 +83,109 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-9.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8-9</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>花鲢</t>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>8.5-11</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>33-46</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-57</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>10-10.6</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-39</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
   </si>
   <si>
     <t>7.5-9.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9.5</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>34-45</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-55</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>10-10.5</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>8-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -200,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>100</t>
+    <t>105</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-15</t>
+    <t>18-16-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>91</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -224,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>79</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-33-30</t>
+    <t>35-32-29</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>60</t>
+    <t>65</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>48</t>
+    <t>52</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -275,7 +278,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-12</t>
+    <t>10-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +287,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>7-9</t>
   </si>
 </sst>
 </file>
@@ -2030,34 +2033,34 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>32</v>
@@ -2190,40 +2193,40 @@
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2231,20 +2234,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2277,19 +2280,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2297,19 +2300,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2317,19 +2320,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2337,42 +2340,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2388,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2401,13 +2404,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2417,10 +2420,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2431,13 +2434,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2447,10 +2450,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2458,16 +2461,16 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.25</t>
+    <t>日期:2026.6.26</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,13 +53,13 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-39</t>
+    <t>35-43</t>
   </si>
   <si>
     <t>白鲢</t>
   </si>
   <si>
-    <t>3-4</t>
+    <t>3.5-4.5</t>
   </si>
   <si>
     <t>3</t>
@@ -113,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-11</t>
+    <t>9.5-11</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>33-46</t>
+    <t>33-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-57</t>
+    <t>20-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10-10.6</t>
+    <t>10-10.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -203,7 +203,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>100</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -215,7 +215,7 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>91</t>
+    <t>89</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>79</t>
+    <t>76</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>35-32-29</t>
+    <t>36-33-30</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>65</t>
+    <t>64</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>52</t>
+    <t>50</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -278,7 +278,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>11-13</t>
   </si>
   <si>
     <t>4-6红</t>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.26</t>
+    <t>日期:2026.6.27</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>8-15</t>
   </si>
   <si>
     <t>2</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -83,15 +83,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-9.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>8.5-9.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -128,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>33-45</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -179,13 +182,10 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9.5</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>8-13.5</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>100</t>
+    <t>120</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-16-14</t>
+    <t>19-17-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>89</t>
+    <t>102</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>65-55</t>
+    <t>75-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>88</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-33-30</t>
+    <t>33-30-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>64</t>
+    <t>72</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>50</t>
+    <t>58</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -1901,7 +1901,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1911,7 +1911,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2033,59 +2033,59 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2118,19 +2118,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2138,16 +2138,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2156,19 +2156,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2176,51 +2176,51 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
         <v>56</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
         <v>58</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>77</v>
@@ -2364,7 +2364,7 @@
         <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>79</v>
@@ -2383,7 +2383,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="14.0" customHeight="true">
+    <row r="29" ht="10.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="200" t="s">
         <v>83</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.27</t>
+    <t>日期:2026.6.28</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,13 +53,13 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-43</t>
+    <t>35-44</t>
   </si>
   <si>
     <t>白鲢</t>
   </si>
   <si>
-    <t>3.5-4.5</t>
+    <t>3-4</t>
   </si>
   <si>
     <t>3</t>
@@ -83,105 +83,105 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>9.5-10</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9-10.5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-45</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-56</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>10-10.6</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-40</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-5.5</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
     <t>7.5-9.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9.5-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-45</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>10-10.5</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-5.5</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
@@ -203,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>120</t>
+    <t>112</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>19-17-16</t>
+    <t>18-17-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>93</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>88</t>
+    <t>79</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>33-30-26</t>
+    <t>34-30-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>72</t>
+    <t>70</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -269,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>18-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -1901,7 +1901,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1911,7 +1911,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2033,59 +2033,59 @@
     </row>
     <row r="9" ht="14.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="10.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2118,19 +2118,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2138,16 +2138,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2156,19 +2156,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2176,51 +2176,51 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="111" t="s">
-        <v>25</v>
-      </c>
       <c r="D19" s="112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
         <v>56</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
         <v>58</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="27" ht="14.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>77</v>
@@ -2364,7 +2364,7 @@
         <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>79</v>
@@ -2383,7 +2383,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="10.0" customHeight="true">
+    <row r="29" ht="14.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="34" ht="11.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
         <v>83</v>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="90">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.28</t>
+    <t>日期:2026.6.29</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-15</t>
+    <t>8-14.5</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-44</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-14.5</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -128,9 +128,6 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-45</t>
-  </si>
-  <si>
     <t>银鱼</t>
   </si>
   <si>
@@ -149,13 +146,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10-10.6</t>
+    <t>10.5-11</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>29-40</t>
+    <t>29-39</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -203,13 +200,13 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>112</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-15</t>
+    <t>17-16-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
@@ -221,25 +218,25 @@
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>75-60</t>
+    <t>75-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>79</t>
+    <t>80</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>34-30-27</t>
+    <t>37-33-25</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>72</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -269,16 +266,13 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-20</t>
+    <t>17-19</t>
   </si>
   <si>
     <t>7-9红</t>
   </si>
   <si>
     <t>4-6青</t>
-  </si>
-  <si>
-    <t>11-13</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -2121,16 +2115,16 @@
         <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2138,16 +2132,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2156,19 +2150,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2176,19 +2170,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2196,14 +2190,14 @@
         <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>30</v>
@@ -2214,19 +2208,19 @@
         <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2234,20 +2228,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2280,19 +2274,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2300,19 +2294,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2320,19 +2314,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2340,16 +2334,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2358,24 +2352,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2391,7 +2385,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2404,13 +2398,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2420,10 +2414,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2434,13 +2428,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2450,10 +2444,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2464,13 +2458,13 @@
         <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.29</t>
+    <t>日期:2026.6.30</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14.5</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,81 +53,84 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
+    <t>35-44</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8-9.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>8.5-10</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
     <t>35-45</t>
   </si>
   <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-15</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>8.5-10.5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>9.5-10</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-10.5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
     <t>银鱼</t>
   </si>
   <si>
@@ -200,7 +203,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>105</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -212,31 +215,31 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>75-58</t>
+    <t>70-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>80</t>
+    <t>75</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-33-25</t>
+    <t>40-30-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>72</t>
+    <t>67</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>58</t>
+    <t>57</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -266,7 +269,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-19</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,13 +278,16 @@
     <t>4-6青</t>
   </si>
   <si>
+    <t>10-13</t>
+  </si>
+  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -2115,16 +2121,16 @@
         <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2132,16 +2138,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2150,19 +2156,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2170,19 +2176,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="14.0" customHeight="true">
@@ -2190,14 +2196,14 @@
         <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>30</v>
@@ -2208,19 +2214,19 @@
         <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2228,20 +2234,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2274,19 +2280,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2294,19 +2300,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2314,19 +2320,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2334,16 +2340,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2352,24 +2358,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2385,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2398,13 +2404,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2414,10 +2420,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2428,13 +2434,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2444,10 +2450,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2458,13 +2464,13 @@
         <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.6.30</t>
+    <t>日期:2026.7.1</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>10-11</t>
   </si>
   <si>
     <t>2</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>10-14.5</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8-9.5</t>
+    <t>7.5-9.5</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -101,7 +101,7 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>8.5-10</t>
+    <t>11</t>
   </si>
   <si>
     <t>6</t>
@@ -167,7 +167,7 @@
     <t>蛳螺(养殖)</t>
   </si>
   <si>
-    <t>3-5.5</t>
+    <t>3-6</t>
   </si>
   <si>
     <t>鮰鱼</t>
@@ -179,13 +179,10 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9.5</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>8-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>102</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>17-16-14</t>
+    <t>18-17-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>89</t>
+    <t>88</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-60</t>
+    <t>70-56</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>76</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-30-24</t>
+    <t>36-28-22</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>67</t>
+    <t>70</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>57</t>
+    <t>58</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,7 +266,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>19-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -278,7 +275,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>12-14</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -287,7 +284,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -2217,16 +2214,16 @@
         <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="10.0" customHeight="true">
@@ -2234,20 +2231,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2280,19 +2277,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="14.0" customHeight="true">
@@ -2300,19 +2297,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2320,19 +2317,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="10.0" customHeight="true">
@@ -2340,16 +2337,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2358,24 +2355,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2391,7 +2388,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="172" t="s">
         <v>5</v>
@@ -2404,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="D30" s="178" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="178" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="179"/>
       <c r="F30" s="180"/>
@@ -2420,10 +2417,10 @@
         <v>11</v>
       </c>
       <c r="B31" s="182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185"/>
@@ -2434,13 +2431,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>87</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>88</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2450,10 +2447,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="196"/>
       <c r="E33" s="197"/>
@@ -2464,13 +2461,13 @@
         <v>23</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="201" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="202" t="s">
         <v>90</v>
-      </c>
-      <c r="D34" s="202" t="s">
-        <v>91</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.1</t>
+    <t>日期:2026.7.2</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>10-11</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>2</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-10</t>
   </si>
   <si>
     <t>4</t>
@@ -83,102 +83,102 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-45</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-56</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>10.5-11</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-40</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
   </si>
   <si>
     <t>7.5-9.5</t>
   </si>
   <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-45</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>10.5-11</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-39</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-6</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
@@ -200,7 +200,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>108</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -212,25 +212,25 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>88</t>
+    <t>93</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-56</t>
+    <t>70-55</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>78</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-28-22</t>
+    <t>37-30-28</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -245,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>58</t>
+    <t>57</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -254,6 +254,54 @@
     <t>35</t>
   </si>
   <si>
+    <t>螃蟹类批发价格:</t>
+  </si>
+  <si>
+    <t>公</t>
+  </si>
+  <si>
+    <t>蟹</t>
+  </si>
+  <si>
+    <t>母</t>
+  </si>
+  <si>
+    <t>规格(两)</t>
+  </si>
+  <si>
+    <t>40-45</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>25-30</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>50-55</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>65-70</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>3.5-3.9</t>
+  </si>
+  <si>
     <t>龙虾类批发价格:</t>
   </si>
   <si>
@@ -266,7 +314,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>19-22</t>
+    <t>25-28</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -275,7 +323,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-14</t>
+    <t>14-17</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -284,7 +332,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>10-13</t>
   </si>
 </sst>
 </file>
@@ -292,13 +340,188 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="152">
+  <fonts count="187">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1266,7 +1489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -1784,14 +2007,14 @@
     <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -1802,40 +2025,40 @@
     <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -1844,17 +2067,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1862,20 +2085,200 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1887,13 +2290,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="10.43359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.48046875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="5.9296875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.25" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="12.25" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
@@ -1948,7 +2351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.0" customHeight="true">
+    <row r="5" ht="10.0" customHeight="true">
       <c r="A5" s="25" t="s">
         <v>6</v>
       </c>
@@ -2028,18 +2431,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" ht="14.0" customHeight="true">
+    <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
       </c>
       <c r="E9" s="53" t="s">
         <v>28</v>
@@ -2048,7 +2451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2063,26 +2466,26 @@
         <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="F11" s="66"/>
+    </row>
+    <row r="12" ht="14.0" customHeight="true">
+      <c r="A12" s="67" t="s">
         <v>35</v>
-      </c>
-      <c r="F11" s="66"/>
-    </row>
-    <row r="12" ht="10.0" customHeight="true">
-      <c r="A12" s="67" t="s">
-        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2115,19 +2518,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2135,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
-    <row r="16" ht="14.0" customHeight="true">
+    <row r="16" ht="10.0" customHeight="true">
       <c r="A16" s="91" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2173,34 +2576,34 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="102" t="s">
+    </row>
+    <row r="18" ht="10.0" customHeight="true">
+      <c r="A18" s="103" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="104" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="18" ht="14.0" customHeight="true">
-      <c r="A18" s="103" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="104" t="s">
-        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>30</v>
@@ -2211,10 +2614,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>25</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
@@ -2226,9 +2629,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" ht="10.0" customHeight="true">
+    <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
         <v>57</v>
@@ -2252,7 +2655,7 @@
       <c r="E21" s="125"/>
       <c r="F21" s="126"/>
     </row>
-    <row r="22" ht="14.0" customHeight="true">
+    <row r="22" ht="10.0" customHeight="true">
       <c r="A22" s="127" t="s">
         <v>3</v>
       </c>
@@ -2292,7 +2695,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" ht="14.0" customHeight="true">
+    <row r="24" ht="10.0" customHeight="true">
       <c r="A24" s="139" t="s">
         <v>11</v>
       </c>
@@ -2332,7 +2735,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" ht="10.0" customHeight="true">
+    <row r="26" ht="14.0" customHeight="true">
       <c r="A26" s="151" t="s">
         <v>21</v>
       </c>
@@ -2350,9 +2753,9 @@
       </c>
       <c r="F26" s="156"/>
     </row>
-    <row r="27" ht="14.0" customHeight="true">
+    <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>76</v>
@@ -2361,7 +2764,7 @@
         <v>77</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>78</v>
@@ -2380,121 +2783,281 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="14.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="173" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="174"/>
+    </row>
+    <row r="30" ht="10.0" customHeight="true">
+      <c r="A30" s="175"/>
+      <c r="B30" s="176" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="177" t="s">
         <v>5</v>
-      </c>
-      <c r="E29" s="173"/>
-      <c r="F29" s="174"/>
-    </row>
-    <row r="30" ht="14.0" customHeight="true">
-      <c r="A30" s="175" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="176" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="177" t="s">
-        <v>83</v>
       </c>
       <c r="D30" s="178" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="179"/>
+      <c r="E30" s="179" t="s">
+        <v>5</v>
+      </c>
       <c r="F30" s="180"/>
     </row>
     <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="182" t="s">
         <v>11</v>
-      </c>
-      <c r="B31" s="182" t="s">
-        <v>82</v>
       </c>
       <c r="C31" s="183" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="184"/>
-      <c r="E31" s="185"/>
+      <c r="D31" s="184" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="185" t="s">
+        <v>87</v>
+      </c>
       <c r="F31" s="186"/>
     </row>
-    <row r="32" ht="10.0" customHeight="true">
+    <row r="32" ht="14.0" customHeight="true">
       <c r="A32" s="187" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
     <row r="33" ht="14.0" customHeight="true">
       <c r="A33" s="193" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="196"/>
+        <v>91</v>
+      </c>
+      <c r="D33" s="196" t="s">
+        <v>11</v>
+      </c>
       <c r="E33" s="197"/>
       <c r="F33" s="198"/>
     </row>
-    <row r="34" ht="11.0" customHeight="true">
+    <row r="34" ht="14.0" customHeight="true">
       <c r="A34" s="199" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="201" t="s">
-        <v>89</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
     </row>
-    <row r="35">
-      <c r="A35" s="205"/>
-      <c r="B35" s="205"/>
-      <c r="C35" s="205"/>
-      <c r="D35" s="205"/>
-      <c r="E35" s="205"/>
-      <c r="F35" s="205"/>
+    <row r="35" ht="14.0" customHeight="true">
+      <c r="A35" s="205" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="206" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="207"/>
+      <c r="D35" s="208" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="209"/>
+      <c r="F35" s="210"/>
+    </row>
+    <row r="36" ht="14.0" customHeight="true">
+      <c r="A36" s="211" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="212" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="213"/>
+      <c r="D36" s="214" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="215"/>
+      <c r="F36" s="216"/>
+    </row>
+    <row r="37" ht="14.0" customHeight="true">
+      <c r="A37" s="217" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="218" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="219"/>
+      <c r="D37" s="220" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="221"/>
+      <c r="F37" s="222"/>
+    </row>
+    <row r="38" ht="10.0" customHeight="true">
+      <c r="A38" s="223" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="224"/>
+      <c r="C38" s="225"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="227"/>
+      <c r="F38" s="228"/>
+    </row>
+    <row r="39" ht="14.0" customHeight="true">
+      <c r="A39" s="229" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="230" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="231" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="232"/>
+      <c r="E39" s="233" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="234"/>
+    </row>
+    <row r="40" ht="14.0" customHeight="true">
+      <c r="A40" s="235" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="236" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="237" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="238"/>
+      <c r="E40" s="239" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" s="240"/>
+    </row>
+    <row r="41" ht="14.0" customHeight="true">
+      <c r="A41" s="241" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="242" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="243" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="244"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="246"/>
+    </row>
+    <row r="42" ht="10.0" customHeight="true">
+      <c r="A42" s="247" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="248" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="249" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="250"/>
+      <c r="E42" s="251" t="s">
+        <v>103</v>
+      </c>
+      <c r="F42" s="252"/>
+    </row>
+    <row r="43" ht="14.0" customHeight="true">
+      <c r="A43" s="253" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="254" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="255" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="256"/>
+      <c r="E43" s="257"/>
+      <c r="F43" s="258"/>
+    </row>
+    <row r="44" ht="11.0" customHeight="true">
+      <c r="A44" s="259" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="260" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="261" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="262"/>
+      <c r="E44" s="263" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="264"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="265"/>
+      <c r="B45" s="265"/>
+      <c r="C45" s="265"/>
+      <c r="D45" s="265"/>
+      <c r="E45" s="265"/>
+      <c r="F45" s="265"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="23">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A45:F45"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.2</t>
+    <t>日期:2026.7.4</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>8-13</t>
   </si>
   <si>
     <t>2</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -83,36 +83,39 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
+    <t>8.5-9.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
     <t>8.5-9</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
     <t>鳊鱼</t>
   </si>
   <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
     <t>9.5-11</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -200,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>150</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-15</t>
+    <t>19-17-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>127</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -224,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>98</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-30-28</t>
+    <t>37-32-25</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>82</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>57</t>
+    <t>68</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -2301,7 +2304,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2314,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2433,16 +2436,16 @@
     </row>
     <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" s="52" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E9" s="53" t="s">
         <v>28</v>
@@ -2451,7 +2454,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2466,26 +2469,26 @@
         <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2518,19 +2521,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2538,16 +2541,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2556,19 +2559,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2576,34 +2579,34 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
         <v>30</v>
@@ -2614,40 +2617,40 @@
         <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2680,19 +2683,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2700,19 +2703,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2720,19 +2723,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2740,42 +2743,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2783,41 +2786,41 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="19.0" customHeight="true">
+    <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>83</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2825,13 +2828,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2840,13 +2843,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2859,7 +2862,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2872,25 +2875,25 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
     </row>
     <row r="35" ht="14.0" customHeight="true">
       <c r="A35" s="205" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B35" s="206" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2900,7 +2903,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2911,21 +2914,21 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="218" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
+    <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2933,7 +2936,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="14.0" customHeight="true">
+    <row r="39" ht="10.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2941,7 +2944,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2954,14 +2957,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2970,10 +2973,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2984,14 +2987,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3000,10 +3003,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3011,17 +3014,17 @@
     </row>
     <row r="44" ht="11.0" customHeight="true">
       <c r="A44" s="259" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.4</t>
+    <t>日期:2026.7.5</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-13</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3-4</t>
+    <t>3-3.5</t>
   </si>
   <si>
     <t>3</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>8.5-9.5</t>
+    <t>7.5-8.5</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -101,7 +101,7 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>9-10.5</t>
   </si>
   <si>
     <t>6</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10.5-11</t>
+    <t>10.2-10.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>150</t>
+    <t>140</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>19-17-16</t>
+    <t>19-18-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>127</t>
+    <t>118</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-55</t>
+    <t>72-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>98</t>
+    <t>90</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-32-25</t>
+    <t>37-33-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>82</t>
+    <t>80</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -272,30 +272,33 @@
     <t>规格(两)</t>
   </si>
   <si>
+    <t>30-35</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>22-25</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
     <t>40-45</t>
   </si>
   <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>25-30</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>50-55</t>
-  </si>
-  <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>65-70</t>
+    <t>55-65</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
+    <t>68-75</t>
+  </si>
+  <si>
     <t>2.8</t>
   </si>
   <si>
@@ -317,7 +320,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>25-28</t>
+    <t>19-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,7 +329,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>14-17</t>
+    <t>12-14</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -335,7 +338,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -343,13 +346,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="187">
+  <fonts count="188">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -2094,26 +2102,20 @@
     <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2121,17 +2123,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2139,17 +2141,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2157,10 +2159,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2178,51 +2186,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2232,33 +2240,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2268,19 +2276,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2304,7 +2312,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2322,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2454,7 +2462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2786,7 +2794,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="18.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2820,7 +2828,7 @@
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2877,7 +2885,9 @@
       <c r="B34" s="200" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="201"/>
+      <c r="C34" s="201" t="s">
+        <v>94</v>
+      </c>
       <c r="D34" s="202" t="s">
         <v>89</v>
       </c>
@@ -2893,7 +2903,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2903,7 +2913,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2921,14 +2931,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="14.0" customHeight="true">
+    <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2936,7 +2946,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="10.0" customHeight="true">
+    <row r="39" ht="14.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2944,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2957,14 +2967,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2973,10 +2983,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2987,14 +2997,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3003,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3017,14 +3027,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.5</t>
+    <t>日期:2026.7.6</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>8-14.5</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-44</t>
+    <t>37-45</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>10.2-10.7</t>
+    <t>9.8-10.4</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -179,7 +179,7 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9.5</t>
+    <t>7.5-10</t>
   </si>
   <si>
     <t>昂刺鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>140</t>
+    <t>135</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>19-18-16</t>
+    <t>17-16-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>108</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>72-60</t>
+    <t>70-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>92</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-33-26</t>
+    <t>37-32-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>80</t>
+    <t>78</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>65</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,31 +272,31 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>30-35</t>
+    <t>27-32</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>22-25</t>
+    <t>20-25</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>40-45</t>
+    <t>36-40</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>55-65</t>
+    <t>50-60</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>68-75</t>
+    <t>65-75</t>
   </si>
   <si>
     <t>2.8</t>
@@ -320,7 +320,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>19-22</t>
+    <t>20-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -329,7 +329,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-14</t>
+    <t>12-15</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -338,7 +338,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-10</t>
+    <t>7-9</t>
   </si>
 </sst>
 </file>
@@ -2312,7 +2312,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2794,7 +2794,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="19.0" customHeight="true">
+    <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
+    <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
         <v>98</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="14.0" customHeight="true">
+    <row r="39" ht="10.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.6</t>
+    <t>日期:2026.7.7</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14.5</t>
+    <t>8-13</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>37-45</t>
+    <t>35-48</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -83,15 +83,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -101,7 +104,7 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>9-10.5</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>6</t>
@@ -179,13 +182,13 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-10</t>
+    <t>7.5-9.5</t>
   </si>
   <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>8-13.5</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,13 +206,13 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>135</t>
+    <t>130</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>17-16-14</t>
+    <t>18-17-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
@@ -221,19 +224,19 @@
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58</t>
+    <t>70-57</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>92</t>
+    <t>90</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-32-27</t>
+    <t>38-33-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -272,7 +275,7 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>27-32</t>
+    <t>30-35</t>
   </si>
   <si>
     <t>1.5</t>
@@ -284,19 +287,19 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>36-40</t>
+    <t>40-45</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>50-60</t>
+    <t>50-55</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>65-75</t>
+    <t>60-70</t>
   </si>
   <si>
     <t>2.8</t>
@@ -320,7 +323,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>20-22</t>
+    <t>19-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -329,7 +332,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-15</t>
+    <t>12-14</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -2312,7 +2315,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2325,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2444,59 +2447,59 @@
     </row>
     <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="10.0" customHeight="true">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2529,19 +2532,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2549,16 +2552,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2567,19 +2570,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2587,78 +2590,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2691,19 +2694,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2711,19 +2714,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2731,19 +2734,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2751,42 +2754,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2794,41 +2797,41 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="18.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>84</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>83</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2836,13 +2839,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2851,13 +2854,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2870,7 +2873,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2883,37 +2886,37 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
     </row>
     <row r="35" ht="14.0" customHeight="true">
       <c r="A35" s="205" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B35" s="206" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2924,21 +2927,21 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" s="218" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="14.0" customHeight="true">
+    <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2946,7 +2949,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="10.0" customHeight="true">
+    <row r="39" ht="14.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2954,7 +2957,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2967,14 +2970,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2983,10 +2986,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2997,14 +3000,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3013,10 +3016,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3024,17 +3027,17 @@
     </row>
     <row r="44" ht="11.0" customHeight="true">
       <c r="A44" s="259" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.7</t>
+    <t>日期:2026.7.8</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-13</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-48</t>
+    <t>35-46</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -83,16 +83,13 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>7.5-9</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -104,7 +101,7 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>10-11</t>
   </si>
   <si>
     <t>6</t>
@@ -131,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-45</t>
+    <t>35-50</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -143,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-56</t>
+    <t>20-58</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -152,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.8-10.4</t>
+    <t>9.2-9.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -206,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>基围虾(大中小)</t>
+  </si>
+  <si>
+    <t>18-17-14</t>
+  </si>
+  <si>
+    <t>河虾(130头)</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>基围虾(大中小)</t>
-  </si>
-  <si>
-    <t>18-17-15</t>
-  </si>
-  <si>
-    <t>河虾(130头)</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-57</t>
+    <t>70-55</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>102</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>38-33-26</t>
+    <t>37-32-26</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>88</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -251,13 +248,13 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>65</t>
+    <t>69</t>
   </si>
   <si>
     <t>黑虎虾</t>
   </si>
   <si>
-    <t>35</t>
+    <t>37</t>
   </si>
   <si>
     <t>螃蟹类批发价格:</t>
@@ -299,7 +296,7 @@
     <t>3.5</t>
   </si>
   <si>
-    <t>60-70</t>
+    <t>60-65</t>
   </si>
   <si>
     <t>2.8</t>
@@ -323,7 +320,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>19-22</t>
+    <t>18-21</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -2447,59 +2444,59 @@
     </row>
     <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2532,19 +2529,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2552,16 +2549,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2570,19 +2567,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2590,78 +2587,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="D19" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2694,19 +2691,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>65</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2714,19 +2711,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>67</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>69</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2734,19 +2731,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>73</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2754,42 +2751,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="159" t="s">
+      <c r="D27" s="160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="161" t="s">
+      <c r="F27" s="162" t="s">
         <v>80</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2802,29 +2799,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="171" t="s">
+      <c r="D29" s="172" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="172" t="s">
-        <v>85</v>
-      </c>
       <c r="E29" s="173" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2839,13 +2836,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="E31" s="185" t="s">
         <v>88</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>89</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2854,13 +2851,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="189" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="189" t="s">
+      <c r="D32" s="190" t="s">
         <v>91</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>92</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2873,7 +2870,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2886,37 +2883,37 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="201" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="201" t="s">
-        <v>95</v>
-      </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
     </row>
     <row r="35" ht="14.0" customHeight="true">
       <c r="A35" s="205" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B35" s="206" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2927,21 +2924,21 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="218" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2957,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2970,14 +2967,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="237" t="s">
         <v>101</v>
-      </c>
-      <c r="C40" s="237" t="s">
-        <v>102</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2986,10 +2983,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -3000,14 +2997,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3016,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3027,17 +3024,17 @@
     </row>
     <row r="44" ht="11.0" customHeight="true">
       <c r="A44" s="259" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.8</t>
+    <t>日期:2026.7.9</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,13 +53,13 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-46</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>白鲢</t>
   </si>
   <si>
-    <t>3-3.5</t>
+    <t>3-4</t>
   </si>
   <si>
     <t>3</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-11</t>
   </si>
   <si>
     <t>4</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-50</t>
+    <t>37-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-58</t>
+    <t>20-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.2-9.7</t>
+    <t>9.4-9.8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,7 +185,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>10-14</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>155</t>
+    <t>138</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-14</t>
+    <t>17-16-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>130</t>
+    <t>116</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-55</t>
+    <t>70-57</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>93</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-32-26</t>
+    <t>35-30-23</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>88</t>
+    <t>80</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,15 +248,12 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>69</t>
+    <t>62</t>
   </si>
   <si>
     <t>黑虎虾</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>螃蟹类批发价格:</t>
   </si>
   <si>
@@ -284,19 +281,19 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>40-45</t>
+    <t>40-50</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>50-55</t>
+    <t>55-65</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>60-65</t>
+    <t>70-75</t>
   </si>
   <si>
     <t>2.8</t>
@@ -320,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-21</t>
+    <t>19-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -329,7 +326,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-14</t>
+    <t>12-15</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -346,18 +343,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="188">
+  <fonts count="187">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1985,91 +1977,109 @@
     <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2078,16 +2088,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2096,16 +2106,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2114,16 +2124,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2132,16 +2142,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2150,17 +2160,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -2171,124 +2181,106 @@
     <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2780,13 +2772,11 @@
       <c r="E27" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
-      </c>
+      <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2799,29 +2789,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="171" t="s">
+      <c r="D29" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="172" t="s">
-        <v>84</v>
-      </c>
       <c r="E29" s="173" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2836,13 +2826,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="E31" s="185" t="s">
         <v>87</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2851,13 +2841,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="189" t="s">
+      <c r="D32" s="190" t="s">
         <v>90</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2870,7 +2860,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2883,13 +2873,13 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="201" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="201" t="s">
-        <v>94</v>
-      </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2903,7 +2893,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2913,7 +2903,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2931,14 +2921,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2954,7 +2944,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2967,14 +2957,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="237" t="s">
         <v>100</v>
-      </c>
-      <c r="C40" s="237" t="s">
-        <v>101</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2983,10 +2973,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2997,14 +2987,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3013,10 +3003,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3027,14 +3017,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.9</t>
+    <t>日期:2026.7.10</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-14</t>
+    <t>8-13</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-45</t>
+    <t>35-46</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-11</t>
+    <t>9-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -89,19 +89,16 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-9</t>
+    <t>8.5-9</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>10-11</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>6</t>
@@ -149,7 +146,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.4-9.8</t>
+    <t>9.5-10</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,7 +182,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>138</t>
+    <t>132</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>17-16-14</t>
+    <t>18-16-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>112</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-57</t>
+    <t>70-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>90</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>35-30-23</t>
+    <t>36-33-25</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>80</t>
+    <t>78</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,12 +245,15 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>62</t>
+    <t>60</t>
   </si>
   <si>
     <t>黑虎虾</t>
   </si>
   <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>螃蟹类批发价格:</t>
   </si>
   <si>
@@ -275,25 +275,25 @@
     <t>1.5</t>
   </si>
   <si>
-    <t>20-25</t>
+    <t>18-22</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>40-50</t>
+    <t>38-45</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>55-65</t>
+    <t>50-55</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>70-75</t>
+    <t>60-70</t>
   </si>
   <si>
     <t>2.8</t>
@@ -317,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>19-22</t>
+    <t>18-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,16 +326,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-15</t>
-  </si>
-  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>7-9</t>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -343,13 +340,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="187">
+  <fonts count="188">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1977,91 +1979,109 @@
     <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2070,16 +2090,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2088,16 +2108,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2106,16 +2126,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2124,16 +2144,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2142,17 +2162,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -2160,127 +2180,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2442,53 +2444,53 @@
         <v>26</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="54" t="s">
         <v>28</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2521,19 +2523,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2541,16 +2543,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2559,19 +2561,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2579,19 +2581,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" s="102" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
@@ -2599,58 +2601,58 @@
         <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="D19" s="112" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="112" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2683,19 +2685,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2703,19 +2705,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2723,19 +2725,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2743,16 +2745,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2761,18 +2763,20 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="162"/>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
@@ -2900,7 +2904,7 @@
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="212" t="s">
         <v>95</v>
@@ -2914,7 +2918,7 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="218" t="s">
         <v>23</v>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3006,7 +3010,7 @@
         <v>99</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3020,11 +3024,11 @@
         <v>99</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="108">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.10</t>
+    <t>日期:2026.7.11</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3-4</t>
+    <t>3-3.5</t>
   </si>
   <si>
     <t>3</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9-10.5</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -89,12 +89,15 @@
     <t>花鲢</t>
   </si>
   <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
     <t>8.5-9</t>
   </si>
   <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
     <t>鳊鱼</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>8.5-11</t>
   </si>
   <si>
     <t>7</t>
@@ -125,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>37-52</t>
+    <t>35-53</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -146,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.5-10</t>
+    <t>9.1-9.6</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -200,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>132</t>
+    <t>158</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-16-15</t>
+    <t>18-17-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>112</t>
+    <t>136</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58</t>
+    <t>70-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>108</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-33-25</t>
+    <t>37-32-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>93</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>60</t>
+    <t>75</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -2444,53 +2447,53 @@
         <v>26</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2523,19 +2526,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2543,16 +2546,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2561,19 +2564,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2581,19 +2584,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
@@ -2601,58 +2604,58 @@
         <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2685,19 +2688,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2705,19 +2708,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2725,19 +2728,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2745,16 +2748,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2763,24 +2766,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2793,29 +2796,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>83</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2830,13 +2833,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2845,13 +2848,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2864,7 +2867,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2877,13 +2880,13 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2897,17 +2900,17 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2918,21 +2921,21 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="218" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
+    <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2940,7 +2943,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="14.0" customHeight="true">
+    <row r="39" ht="10.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2961,14 +2964,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2977,10 +2980,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2991,14 +2994,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3007,10 +3010,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3021,14 +3024,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.11</t>
+    <t>日期:2026.7.12</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3-3.5</t>
+    <t>3-4</t>
   </si>
   <si>
     <t>3</t>
@@ -83,15 +83,18 @@
     <t>鲤鱼</t>
   </si>
   <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
     <t>非洲鲫鱼</t>
   </si>
   <si>
@@ -113,7 +116,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-11</t>
+    <t>9.5-10.5</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +131,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-53</t>
+    <t>35-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,13 +152,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.1-9.6</t>
+    <t>9.2-9.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>29-40</t>
+    <t>29-42</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -185,7 +188,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>8-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -215,31 +218,31 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>136</t>
+    <t>132</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-60</t>
+    <t>73-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>102</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-32-27</t>
+    <t>37-30-25</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>88</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +251,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>65</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,31 +275,31 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>30-35</t>
+    <t>27-32</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>18-22</t>
+    <t>18-25</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>38-45</t>
+    <t>36-46</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>50-55</t>
+    <t>48-60</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>60-70</t>
+    <t>65-75</t>
   </si>
   <si>
     <t>2.8</t>
@@ -320,7 +323,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-20</t>
+    <t>17-20</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -2309,7 +2312,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2319,7 +2322,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2441,59 +2444,59 @@
     </row>
     <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="14.0" customHeight="true">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2526,19 +2529,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2546,16 +2549,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2564,19 +2567,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2584,78 +2587,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2688,19 +2691,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2708,19 +2711,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2728,19 +2731,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2748,42 +2751,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2791,41 +2794,41 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="19.0" customHeight="true">
+    <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>84</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>83</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2833,13 +2836,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2848,13 +2851,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2867,7 +2870,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2880,37 +2883,37 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
     </row>
     <row r="35" ht="14.0" customHeight="true">
       <c r="A35" s="205" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B35" s="206" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2921,21 +2924,21 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" s="218" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2951,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2964,14 +2967,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2980,10 +2983,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2994,14 +2997,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3010,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3021,17 +3024,17 @@
     </row>
     <row r="44" ht="11.0" customHeight="true">
       <c r="A44" s="259" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.12</t>
+    <t>日期:2026.7.13</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-46</t>
+    <t>35-47</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-14.5</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -152,13 +152,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.2-9.7</t>
+    <t>9.2-9.8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>29-42</t>
+    <t>29-40</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -206,43 +206,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>158</t>
+    <t>150</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-15</t>
+    <t>20-18-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>132</t>
+    <t>135</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>73-60</t>
+    <t>70-58</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>108</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-30-25</t>
+    <t>37-32-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>88</t>
+    <t>87</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -275,31 +275,31 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>27-32</t>
+    <t>32-40</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>18-25</t>
+    <t>27-28</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>36-46</t>
+    <t>45-53</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>48-60</t>
+    <t>56-65</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>65-75</t>
+    <t>70-80</t>
   </si>
   <si>
     <t>2.8</t>
@@ -323,7 +323,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>17-20</t>
+    <t>20-23</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -332,13 +332,16 @@
     <t>4-6青</t>
   </si>
   <si>
+    <t>13-15</t>
+  </si>
+  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -3004,7 +3007,7 @@
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3016,7 +3019,7 @@
         <v>101</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3030,11 +3033,11 @@
         <v>101</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.13</t>
+    <t>日期:2026.7.14</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>35-47</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>10-14.5</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -83,16 +83,13 @@
     <t>鲤鱼</t>
   </si>
   <si>
-    <t>5-6</t>
+    <t>5</t>
   </si>
   <si>
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>7.5-9</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -104,9 +101,6 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>9-11</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -116,7 +110,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-10.5</t>
+    <t>8.5-11</t>
   </si>
   <si>
     <t>7</t>
@@ -188,7 +182,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>8-13.5</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -206,19 +200,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>150</t>
+    <t>160</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-16</t>
+    <t>18-17-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>135</t>
+    <t>132</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -236,7 +230,7 @@
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-32-27</t>
+    <t>37-30-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
@@ -251,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>65</t>
+    <t>70</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -275,31 +269,31 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>32-40</t>
+    <t>25-45</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>27-28</t>
+    <t>21-35</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>45-53</t>
+    <t>35-55</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>56-65</t>
+    <t>45-65</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>70-80</t>
+    <t>55-75</t>
   </si>
   <si>
     <t>2.8</t>
@@ -323,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>20-23</t>
+    <t>22-25</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -332,16 +326,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>13-15</t>
+    <t>14-17</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
-  </si>
-  <si>
-    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -349,18 +340,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="188">
+  <fonts count="187">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1664,203 +1650,221 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1868,211 +1872,211 @@
     <xf numFmtId="0" fontId="93" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2081,16 +2085,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2099,16 +2103,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2117,16 +2121,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2135,16 +2139,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2153,17 +2157,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -2174,124 +2178,106 @@
     <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2447,59 +2433,57 @@
     </row>
     <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>30</v>
-      </c>
+      <c r="F9" s="54"/>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="59" t="s">
-        <v>33</v>
-      </c>
       <c r="F10" s="60" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2532,19 +2516,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2552,16 +2536,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
@@ -2570,19 +2554,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2590,78 +2574,78 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
       <c r="A18" s="103" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="D19" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="113" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2694,19 +2678,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2714,19 +2698,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2734,19 +2718,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2754,42 +2738,42 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="159" t="s">
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="D27" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="161" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2802,29 +2786,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="171" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="171" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="172" t="s">
-        <v>85</v>
-      </c>
       <c r="E29" s="173" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2839,13 +2823,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="184" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="185" t="s">
         <v>87</v>
-      </c>
-      <c r="D31" s="184" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>89</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2854,13 +2838,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="189" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>90</v>
-      </c>
-      <c r="C32" s="189" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>92</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2873,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2886,37 +2870,37 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
     </row>
     <row r="35" ht="14.0" customHeight="true">
       <c r="A35" s="205" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B35" s="206" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2927,21 +2911,21 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B37" s="218" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2957,7 +2941,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2970,14 +2954,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2986,10 +2970,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -3000,14 +2984,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3016,10 +3000,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3027,17 +3011,17 @@
     </row>
     <row r="44" ht="11.0" customHeight="true">
       <c r="A44" s="259" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.14</t>
+    <t>日期:2026.7.15</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>9.5-11.5</t>
   </si>
   <si>
     <t>4</t>
@@ -110,7 +110,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-11</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>7</t>
@@ -146,13 +146,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.2-9.8</t>
+    <t>9.3-9.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>29-40</t>
+    <t>29-39</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -182,7 +182,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>8-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -200,7 +200,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>160</t>
+    <t>150</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -212,31 +212,31 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>132</t>
+    <t>123</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-58</t>
+    <t>70-60</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>102</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-30-24</t>
+    <t>36-31-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>88</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -269,31 +269,31 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>25-45</t>
+    <t>27-43</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>21-35</t>
+    <t>20-33</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>35-55</t>
+    <t>37-53</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>45-65</t>
+    <t>45-63</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>55-75</t>
+    <t>53-73</t>
   </si>
   <si>
     <t>2.8</t>
@@ -317,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>22-25</t>
+    <t>21-24</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,7 +326,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>14-17</t>
+    <t>13-16</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -340,13 +340,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="187">
+  <fonts count="188">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1650,415 +1655,433 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2067,16 +2090,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2085,16 +2108,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2103,16 +2126,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2121,16 +2144,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2139,17 +2162,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
@@ -2157,127 +2180,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2447,7 +2452,9 @@
       <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="54"/>
+      <c r="F9" s="54" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
@@ -3021,7 +3028,7 @@
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="108">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.15</t>
+    <t>日期:2026.7.16</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>9.5-11.5</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -101,6 +101,9 @@
     <t>鳊鱼</t>
   </si>
   <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>8.5-9.5</t>
   </si>
   <si>
     <t>7</t>
@@ -125,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-52</t>
+    <t>35-54</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -146,13 +149,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.3-9.7</t>
+    <t>9.3-9.8</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>29-39</t>
+    <t>29-40</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -206,13 +209,13 @@
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-14</t>
+    <t>17-16-13</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>123</t>
+    <t>128</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -230,13 +233,13 @@
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-31-24</t>
+    <t>36-30-20</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>88</t>
+    <t>87</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>66</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,31 +272,28 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>27-43</t>
-  </si>
-  <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>20-33</t>
+    <t>23-30</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>37-53</t>
+    <t>45-55</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>45-63</t>
+    <t>55-65</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>53-73</t>
+    <t>65-75</t>
   </si>
   <si>
     <t>2.8</t>
@@ -326,13 +326,16 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>13-16</t>
+    <t>12-15</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
+  </si>
+  <si>
+    <t>8-11</t>
   </si>
 </sst>
 </file>
@@ -2306,7 +2309,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2316,7 +2319,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2453,44 +2456,44 @@
         <v>28</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="10.0" customHeight="true">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.0" customHeight="true">
       <c r="A11" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2523,19 +2526,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2543,37 +2546,37 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="90"/>
     </row>
-    <row r="16" ht="10.0" customHeight="true">
+    <row r="16" ht="14.0" customHeight="true">
       <c r="A16" s="91" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="14.0" customHeight="true">
@@ -2581,19 +2584,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="10.0" customHeight="true">
@@ -2601,58 +2604,58 @@
         <v>23</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2685,19 +2688,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2705,19 +2708,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2725,19 +2728,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2745,16 +2748,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2763,24 +2766,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2788,41 +2791,41 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="18.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>83</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2830,7 +2833,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D31" s="184" t="s">
         <v>86</v>
@@ -2904,7 +2907,7 @@
     </row>
     <row r="36" ht="14.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
         <v>95</v>
@@ -2918,7 +2921,7 @@
     </row>
     <row r="37" ht="14.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="218" t="s">
         <v>23</v>
@@ -2930,7 +2933,7 @@
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="14.0" customHeight="true">
+    <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
         <v>97</v>
       </c>
@@ -2940,7 +2943,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="10.0" customHeight="true">
+    <row r="39" ht="14.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -3028,7 +3031,7 @@
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.16</t>
+    <t>日期:2026.7.18</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-9</t>
+    <t>7.5-8.5</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -113,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>8.5-9.5</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-54</t>
+    <t>35-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.3-9.8</t>
+    <t>9.2-9.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,7 +185,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>8-13.5</t>
+    <t>10-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>150</t>
+    <t>170</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>17-16-13</t>
+    <t>20-18-16</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>128</t>
+    <t>145</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>70-60</t>
+    <t>65-55</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>102</t>
+    <t>106</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-30-20</t>
+    <t>40-33-27</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>87</t>
+    <t>90</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>66</t>
+    <t>78</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,10 +272,13 @@
     <t>规格(两)</t>
   </si>
   <si>
+    <t>32-42</t>
+  </si>
+  <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>23-30</t>
+    <t>18-28</t>
   </si>
   <si>
     <t>2.5</t>
@@ -317,7 +320,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>21-24</t>
+    <t>18-23</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,7 +329,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-15</t>
+    <t>9-15</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -335,7 +338,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>8-11</t>
+    <t>5-8</t>
   </si>
 </sst>
 </file>
@@ -2309,7 +2312,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2319,7 +2322,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2459,7 +2462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2559,7 +2562,7 @@
       </c>
       <c r="F15" s="90"/>
     </row>
-    <row r="16" ht="14.0" customHeight="true">
+    <row r="16" ht="10.0" customHeight="true">
       <c r="A16" s="91" t="s">
         <v>16</v>
       </c>
@@ -2791,7 +2794,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="19.0" customHeight="true">
+    <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2825,7 +2828,7 @@
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2833,13 +2836,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2848,13 +2851,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2867,7 +2870,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2880,13 +2883,13 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="201" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2900,7 +2903,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2910,7 +2913,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2928,14 +2931,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
+    <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2943,7 +2946,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="14.0" customHeight="true">
+    <row r="39" ht="10.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2951,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2964,14 +2967,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2980,10 +2983,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2994,14 +2997,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3010,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3024,14 +3027,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.18</t>
+    <t>日期:2026.7.19</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-8.5</t>
+    <t>7.5-9</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -113,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>9-10.5</t>
   </si>
   <si>
     <t>7</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-56</t>
+    <t>20-54</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.2-9.7</t>
+    <t>9.7-10.3</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,7 +185,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-13.5</t>
+    <t>8-13.5</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>170</t>
+    <t>150</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>20-18-16</t>
+    <t>18-17-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>145</t>
+    <t>123</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>65-55</t>
+    <t>60-50</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>106</t>
+    <t>102</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-33-27</t>
+    <t>37-32-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>89</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -254,7 +254,7 @@
     <t>黑虎虾</t>
   </si>
   <si>
-    <t>37</t>
+    <t>35</t>
   </si>
   <si>
     <t>螃蟹类批发价格:</t>
@@ -272,13 +272,13 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>32-42</t>
+    <t>30-42</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>18-28</t>
+    <t>20-30</t>
   </si>
   <si>
     <t>2.5</t>
@@ -290,13 +290,13 @@
     <t>1.8</t>
   </si>
   <si>
-    <t>55-65</t>
+    <t>60-70</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>65-75</t>
+    <t>70-80</t>
   </si>
   <si>
     <t>2.8</t>
@@ -320,7 +320,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>18-23</t>
+    <t>20-22</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -329,7 +329,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>9-15</t>
+    <t>12-14</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -338,7 +338,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>5-8</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -2312,7 +2312,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2794,7 +2794,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="18.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="14.0" customHeight="true">
+    <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
         <v>98</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="10.0" customHeight="true">
+    <row r="39" ht="14.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.19</t>
+    <t>日期:2026.7.21</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,228 +53,225 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
+    <t>37-47</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>3.5-4.5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>10-14.5</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>7.5-9.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-52</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-54</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>9.7-10.4</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-40</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
+    <t>昂刺鱼</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>清江鱼</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>梭子蟹(大中小)</t>
+  </si>
+  <si>
+    <t>虾类批发价格:</t>
+  </si>
+  <si>
+    <t>河虾(100头)</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>基围虾(大中小)</t>
+  </si>
+  <si>
+    <t>17-16-14</t>
+  </si>
+  <si>
+    <t>河虾(130头)</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>白虾(大中小)</t>
+  </si>
+  <si>
+    <t>60-50</t>
+  </si>
+  <si>
+    <t>河虾(150头)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>罗氏虾(大中小)</t>
+  </si>
+  <si>
+    <t>33-28-24</t>
+  </si>
+  <si>
+    <t>河虾(160头)</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>斑节虾</t>
+  </si>
+  <si>
+    <t>河虾(180头)</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>黑虎虾</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>螃蟹类批发价格:</t>
+  </si>
+  <si>
+    <t>公</t>
+  </si>
+  <si>
+    <t>蟹</t>
+  </si>
+  <si>
+    <t>母</t>
+  </si>
+  <si>
+    <t>规格(两)</t>
+  </si>
+  <si>
     <t>35-45</t>
   </si>
   <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-14.5</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>8.5-10.5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-9</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>9.5-11</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9-10.5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-52</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-54</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>9.7-10.3</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-40</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-6</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
-    <t>7.5-9.5</t>
-  </si>
-  <si>
-    <t>昂刺鱼</t>
-  </si>
-  <si>
-    <t>8-13.5</t>
-  </si>
-  <si>
-    <t>清江鱼</t>
-  </si>
-  <si>
-    <t>13.5</t>
-  </si>
-  <si>
-    <t>梭子蟹(大中小)</t>
-  </si>
-  <si>
-    <t>虾类批发价格:</t>
-  </si>
-  <si>
-    <t>河虾(100头)</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>基围虾(大中小)</t>
-  </si>
-  <si>
-    <t>18-17-14</t>
-  </si>
-  <si>
-    <t>河虾(130头)</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>白虾(大中小)</t>
-  </si>
-  <si>
-    <t>60-50</t>
-  </si>
-  <si>
-    <t>河虾(150头)</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>罗氏虾(大中小)</t>
-  </si>
-  <si>
-    <t>37-32-24</t>
-  </si>
-  <si>
-    <t>河虾(160头)</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>斑节虾</t>
-  </si>
-  <si>
-    <t>河虾(180头)</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>黑虎虾</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>螃蟹类批发价格:</t>
-  </si>
-  <si>
-    <t>公</t>
-  </si>
-  <si>
-    <t>蟹</t>
-  </si>
-  <si>
-    <t>母</t>
-  </si>
-  <si>
-    <t>规格(两)</t>
-  </si>
-  <si>
-    <t>30-42</t>
-  </si>
-  <si>
     <t>1.5</t>
   </si>
   <si>
@@ -284,21 +281,18 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>45-55</t>
+    <t>50-60</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>60-70</t>
+    <t>65-75</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>70-80</t>
-  </si>
-  <si>
     <t>2.8</t>
   </si>
   <si>
@@ -320,7 +314,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>20-22</t>
+    <t>28-32</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -329,16 +323,16 @@
     <t>4-6青</t>
   </si>
   <si>
+    <t>15-18</t>
+  </si>
+  <si>
+    <t>4-6红</t>
+  </si>
+  <si>
+    <t>3-5</t>
+  </si>
+  <si>
     <t>12-14</t>
-  </si>
-  <si>
-    <t>4-6红</t>
-  </si>
-  <si>
-    <t>3-5</t>
-  </si>
-  <si>
-    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -346,18 +340,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="188">
+  <fonts count="187">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -2102,20 +2091,26 @@
     <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2123,17 +2118,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2141,17 +2136,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2159,136 +2154,130 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2628,16 +2617,16 @@
         <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="114" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
@@ -2645,20 +2634,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2691,19 +2680,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2711,19 +2700,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2731,19 +2720,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2751,16 +2740,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2769,24 +2758,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2799,29 +2788,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="171" t="s">
+      <c r="D29" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="172" t="s">
-        <v>84</v>
-      </c>
       <c r="E29" s="173" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2836,13 +2825,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="E31" s="185" t="s">
         <v>87</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2851,13 +2840,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="189" t="s">
+      <c r="D32" s="190" t="s">
         <v>90</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2870,7 +2859,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2883,13 +2872,11 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="201" t="s">
-        <v>94</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2903,7 +2890,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2913,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2931,14 +2918,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2954,7 +2941,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2967,14 +2954,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2983,10 +2970,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2997,14 +2984,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3013,10 +3000,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3027,14 +3014,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.21</t>
+    <t>日期:2026.7.22</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3.5-4.5</t>
+    <t>3.5-4</t>
   </si>
   <si>
     <t>3</t>
@@ -89,96 +89,99 @@
     <t>花鲢</t>
   </si>
   <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>9.5-11</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-52</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-56</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>9.7-10.3</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>29-40</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
     <t>7.5-9.5</t>
   </si>
   <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>9-11</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9.5-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-52</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-54</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>9.7-10.4</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>29-40</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-6</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
     <t>昂刺鱼</t>
   </si>
   <si>
@@ -200,7 +203,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>160</t>
+    <t>170</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -212,7 +215,7 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>135</t>
+    <t>146</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -224,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>109</t>
+    <t>118</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>33-28-24</t>
+    <t>36-32-25</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>92</t>
+    <t>99</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>73</t>
+    <t>78</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,30 +272,33 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>35-45</t>
+    <t>30-40</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>20-30</t>
+    <t>20-25</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>50-60</t>
+    <t>48-58</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>65-75</t>
+    <t>60-70</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
+    <t>75-85</t>
+  </si>
+  <si>
     <t>2.8</t>
   </si>
   <si>
@@ -323,7 +329,7 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>15-18</t>
+    <t>15-17</t>
   </si>
   <si>
     <t>4-6红</t>
@@ -332,7 +338,7 @@
     <t>3-5</t>
   </si>
   <si>
-    <t>12-14</t>
+    <t>11-13</t>
   </si>
 </sst>
 </file>
@@ -340,13 +346,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="187">
+  <fonts count="188">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="报宋"/>
+      <sz val="10.0"/>
+      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -2091,26 +2102,20 @@
     <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2118,17 +2123,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2136,17 +2141,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2154,10 +2159,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2175,51 +2186,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2229,33 +2240,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2265,19 +2276,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2617,16 +2628,16 @@
         <v>54</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D19" s="112" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
@@ -2634,20 +2645,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2680,19 +2691,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2700,19 +2711,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2720,19 +2731,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2740,16 +2751,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2758,24 +2769,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2788,29 +2799,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>83</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2825,13 +2836,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2840,13 +2851,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2859,7 +2870,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2872,11 +2883,13 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="201"/>
+        <v>93</v>
+      </c>
+      <c r="C34" s="201" t="s">
+        <v>94</v>
+      </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2890,7 +2903,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2900,7 +2913,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2918,14 +2931,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2941,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2954,14 +2967,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2970,10 +2983,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2984,14 +2997,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3000,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3014,14 +3027,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.22</t>
+    <t>日期:2026.7.23</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-11</t>
   </si>
   <si>
     <t>4</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-52</t>
+    <t>36-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>9.7-10.3</t>
+    <t>7.9-8.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,13 +185,13 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>清江鱼</t>
   </si>
   <si>
-    <t>12.5</t>
+    <t>13.5</t>
   </si>
   <si>
     <t>梭子蟹(大中小)</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>170</t>
+    <t>190</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>17-16-14</t>
+    <t>18-17-13</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>146</t>
+    <t>158</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>60-50</t>
+    <t>65-50</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>121</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>36-32-25</t>
+    <t>38-30-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>99</t>
+    <t>96</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>73</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -284,7 +284,7 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>48-58</t>
+    <t>45-55</t>
   </si>
   <si>
     <t>1.8</t>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>3.5</t>
-  </si>
-  <si>
-    <t>75-85</t>
   </si>
   <si>
     <t>2.8</t>
@@ -346,18 +343,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="188">
+  <fonts count="187">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -2102,20 +2094,26 @@
     <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2123,17 +2121,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2141,17 +2139,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2159,136 +2157,130 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2885,9 +2877,7 @@
       <c r="B34" s="200" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="201" t="s">
-        <v>94</v>
-      </c>
+      <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
         <v>89</v>
       </c>
@@ -2903,7 +2893,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2913,7 +2903,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2931,14 +2921,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2954,7 +2944,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2967,14 +2957,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="237" t="s">
         <v>100</v>
-      </c>
-      <c r="C40" s="237" t="s">
-        <v>101</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2983,10 +2973,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2997,14 +2987,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3013,10 +3003,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3027,14 +3017,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.23</t>
+    <t>日期:2026.7.24</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3.5-4</t>
+    <t>3.5-4.5</t>
   </si>
   <si>
     <t>3</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-11</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.9-8.5</t>
+    <t>7.8-8.3</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,7 +185,7 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>10-17</t>
   </si>
   <si>
     <t>清江鱼</t>
@@ -203,7 +203,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>190</t>
+    <t>195</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -215,7 +215,7 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>158</t>
+    <t>163</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,7 +227,7 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>121</t>
+    <t>125</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
@@ -239,7 +239,7 @@
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>96</t>
+    <t>99</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>73</t>
+    <t>76</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,25 +272,25 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>30-40</t>
+    <t>30-45</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>20-25</t>
+    <t>20-30</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>45-55</t>
+    <t>38-60</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>60-70</t>
+    <t>42-75</t>
   </si>
   <si>
     <t>3.5</t>
@@ -317,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>28-32</t>
+    <t>26-29</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,16 +326,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>15-17</t>
+    <t>13-15</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
-  </si>
-  <si>
-    <t>11-13</t>
   </si>
 </sst>
 </file>
@@ -2304,7 +2301,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2311,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2454,7 +2451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2786,7 +2783,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="19.0" customHeight="true">
+    <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2820,7 +2817,7 @@
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2926,7 +2923,7 @@
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
+    <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
         <v>97</v>
       </c>
@@ -2936,7 +2933,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="14.0" customHeight="true">
+    <row r="39" ht="10.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -3024,7 +3021,7 @@
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.24</t>
+    <t>日期:2026.7.25</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -101,7 +101,7 @@
     <t>鳊鱼</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>9.5-11</t>
   </si>
   <si>
     <t>6</t>
@@ -113,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>9.5-11.5</t>
   </si>
   <si>
     <t>7</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.8-8.3</t>
+    <t>7.8-8.4</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -203,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>195</t>
+    <t>170</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-13</t>
+    <t>17-16-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>163</t>
+    <t>143</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>125</t>
+    <t>112</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>38-30-24</t>
+    <t>40-33-23</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>99</t>
+    <t>93</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>78</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -290,7 +290,7 @@
     <t>1.8</t>
   </si>
   <si>
-    <t>42-75</t>
+    <t>62-75</t>
   </si>
   <si>
     <t>3.5</t>
@@ -317,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>26-29</t>
+    <t>27-30</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,13 +326,16 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>13-15</t>
+    <t>14-16</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
+  </si>
+  <si>
+    <t>10-13</t>
   </si>
 </sst>
 </file>
@@ -3021,7 +3024,7 @@
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.25</t>
+    <t>日期:2026.7.26</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -59,7 +59,7 @@
     <t>白鲢</t>
   </si>
   <si>
-    <t>3.5-4.5</t>
+    <t>3.5-4</t>
   </si>
   <si>
     <t>3</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-8.5</t>
+    <t>7.5-8</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -101,21 +101,21 @@
     <t>鳊鱼</t>
   </si>
   <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
     <t>9.5-11</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9.5-11.5</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>36-52</t>
+    <t>35-52</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,13 +149,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.8-8.4</t>
+    <t>7.8-8.5</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>29-40</t>
+    <t>28-36</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -179,7 +179,7 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9.5</t>
+    <t>7.5-9</t>
   </si>
   <si>
     <t>昂刺鱼</t>
@@ -203,43 +203,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>170</t>
+    <t>190</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>17-16-15</t>
+    <t>18-17-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>143</t>
+    <t>163</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>65-50</t>
+    <t>60-50</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>112</t>
+    <t>125</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>40-33-23</t>
+    <t>37-32-23</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>93</t>
+    <t>108</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>78</t>
+    <t>76</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,7 +272,7 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>30-45</t>
+    <t>35-45</t>
   </si>
   <si>
     <t>1.5</t>
@@ -284,13 +284,13 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>38-60</t>
+    <t>40-58</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>62-75</t>
+    <t>45-68</t>
   </si>
   <si>
     <t>3.5</t>
@@ -317,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>27-30</t>
+    <t>25-30</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,16 +326,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>14-16</t>
+    <t>13-15</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
-  </si>
-  <si>
-    <t>10-13</t>
   </si>
 </sst>
 </file>
@@ -2304,7 +2301,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2311,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2454,7 +2451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2786,7 +2783,7 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="18.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
@@ -2820,7 +2817,7 @@
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2926,7 +2923,7 @@
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="14.0" customHeight="true">
+    <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
         <v>97</v>
       </c>
@@ -2936,7 +2933,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="10.0" customHeight="true">
+    <row r="39" ht="14.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -3024,7 +3021,7 @@
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.26</t>
+    <t>日期:2026.7.28</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-13</t>
+    <t>10-13</t>
   </si>
   <si>
     <t>2</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-10</t>
   </si>
   <si>
     <t>4</t>
@@ -89,7 +89,7 @@
     <t>花鲢</t>
   </si>
   <si>
-    <t>7.5-8</t>
+    <t>7.5-8.5</t>
   </si>
   <si>
     <t>非洲鲫鱼</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-52</t>
+    <t>35-50</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-56</t>
+    <t>20-53</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.8-8.5</t>
+    <t>7.6-8.2</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -179,15 +179,12 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-9</t>
+    <t>7.5-10</t>
   </si>
   <si>
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-17</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -203,19 +200,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>190</t>
+    <t>155</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-17-14</t>
+    <t>16-13-12</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>163</t>
+    <t>128</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -227,19 +224,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>125</t>
+    <t>105</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-32-23</t>
+    <t>37-30-25</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>92</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>75</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,25 +269,25 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>35-45</t>
+    <t>22-45</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>20-30</t>
+    <t>18-30</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>40-58</t>
+    <t>28-55</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>45-68</t>
+    <t>38-75</t>
   </si>
   <si>
     <t>3.5</t>
@@ -317,7 +314,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>25-30</t>
+    <t>20-24</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,13 +323,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>13-15</t>
-  </si>
-  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -2626,7 +2623,7 @@
         <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
@@ -2634,20 +2631,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2680,19 +2677,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2700,19 +2697,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2720,19 +2717,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2740,16 +2737,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2758,24 +2755,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2788,29 +2785,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="171" t="s">
+      <c r="D29" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="172" t="s">
-        <v>84</v>
-      </c>
       <c r="E29" s="173" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2825,13 +2822,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="E31" s="185" t="s">
         <v>87</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2840,13 +2837,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="189" t="s">
+      <c r="D32" s="190" t="s">
         <v>90</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2859,7 +2856,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2872,11 +2869,11 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2890,7 +2887,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2900,7 +2897,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2918,14 +2915,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
     <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2941,7 +2938,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2954,14 +2951,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="237" t="s">
         <v>99</v>
-      </c>
-      <c r="C40" s="237" t="s">
-        <v>100</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2970,10 +2967,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2984,14 +2981,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3000,10 +2997,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3014,14 +3011,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.28</t>
+    <t>日期:2026.7.29</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>10-13</t>
+    <t>8-13</t>
   </si>
   <si>
     <t>2</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10</t>
+    <t>8.5-10.5</t>
   </si>
   <si>
     <t>4</t>
@@ -113,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9.5-11</t>
+    <t>8.5-11</t>
   </si>
   <si>
     <t>7</t>
@@ -140,7 +140,7 @@
     <t>甲鱼(养殖)</t>
   </si>
   <si>
-    <t>20-53</t>
+    <t>20-56</t>
   </si>
   <si>
     <t>海银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.6-8.2</t>
+    <t>7.2-7.7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -179,7 +179,7 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-10</t>
+    <t>7.5-10.5</t>
   </si>
   <si>
     <t>昂刺鱼</t>
@@ -188,7 +188,7 @@
     <t>清江鱼</t>
   </si>
   <si>
-    <t>13.5</t>
+    <t>12.5</t>
   </si>
   <si>
     <t>梭子蟹(大中小)</t>
@@ -200,43 +200,43 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>155</t>
+    <t>160</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>16-13-12</t>
+    <t>18-16-15</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>128</t>
+    <t>132</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>60-50</t>
+    <t>65-52</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>109</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>37-30-25</t>
+    <t>45-37-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>92</t>
+    <t>90</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>75</t>
+    <t>70</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,19 +269,19 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>22-45</t>
+    <t>23-45</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>18-30</t>
+    <t>10-30</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>28-55</t>
+    <t>28-58</t>
   </si>
   <si>
     <t>1.8</t>
@@ -314,7 +314,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>20-24</t>
+    <t>20-25</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -323,13 +323,16 @@
     <t>4-6青</t>
   </si>
   <si>
+    <t>10-14</t>
+  </si>
+  <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -2988,7 +2991,7 @@
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3000,7 +3003,7 @@
         <v>98</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3014,11 +3017,11 @@
         <v>98</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.7.29</t>
+    <t>日期:2026.8.1</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>37-47</t>
+    <t>55-57</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -74,7 +74,7 @@
     <t>草鱼</t>
   </si>
   <si>
-    <t>8.5-10.5</t>
+    <t>8.5-11</t>
   </si>
   <si>
     <t>4</t>
@@ -101,21 +101,21 @@
     <t>鳊鱼</t>
   </si>
   <si>
+    <t>9.5-11.5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
     <t>9-11</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>8.5-11</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-50</t>
+    <t>35-48</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,13 +149,13 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.2-7.7</t>
+    <t>7.6-8.2</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
   </si>
   <si>
-    <t>28-36</t>
+    <t>28-35</t>
   </si>
   <si>
     <t>泥鳅(养殖)</t>
@@ -179,12 +179,15 @@
     <t>黑鱼</t>
   </si>
   <si>
-    <t>7.5-10.5</t>
+    <t>7.5-9.5</t>
   </si>
   <si>
     <t>昂刺鱼</t>
   </si>
   <si>
+    <t>10-17</t>
+  </si>
+  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -200,19 +203,19 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>160</t>
+    <t>180</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
   </si>
   <si>
-    <t>18-16-15</t>
+    <t>18-17-14</t>
   </si>
   <si>
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>132</t>
+    <t>153</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
@@ -224,19 +227,19 @@
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>109</t>
+    <t>118</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>45-37-24</t>
+    <t>43-35-22</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>90</t>
+    <t>95</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -245,7 +248,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>70</t>
+    <t>76</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -269,25 +272,25 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>23-45</t>
+    <t>30-45</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>10-30</t>
+    <t>20-30</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>28-58</t>
+    <t>40-60</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>38-75</t>
+    <t>50-75</t>
   </si>
   <si>
     <t>3.5</t>
@@ -314,7 +317,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>20-25</t>
+    <t>21-27</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -323,16 +326,13 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>12-15</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
-  </si>
-  <si>
-    <t>8-10</t>
   </si>
 </sst>
 </file>
@@ -2301,7 +2301,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2311,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="11.0" customHeight="true">
+    <row r="2" ht="10.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="14.0" customHeight="true">
+    <row r="10" ht="10.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
@@ -2634,20 +2634,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2680,19 +2680,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2700,19 +2700,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2720,19 +2720,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2740,16 +2740,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2758,24 +2758,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="159" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="162" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2783,41 +2783,41 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="19.0" customHeight="true">
+    <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="171" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="173" t="s">
         <v>83</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="14.0" customHeight="true">
+    <row r="31" ht="10.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2825,13 +2825,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="184" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" s="185" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2840,13 +2840,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="189" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="190" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2859,7 +2859,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2872,11 +2872,11 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2900,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
+    <row r="38" ht="14.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2933,7 +2933,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="14.0" customHeight="true">
+    <row r="39" ht="10.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2954,14 +2954,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C40" s="237" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2970,10 +2970,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2984,14 +2984,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3000,10 +3000,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3014,14 +3014,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="F44" s="264"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -17,7 +17,7 @@
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.8.1</t>
+    <t>日期:2026.8.8</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -44,7 +44,7 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>8-13</t>
+    <t>8-14</t>
   </si>
   <si>
     <t>2</t>
@@ -53,7 +53,7 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
-    <t>55-57</t>
+    <t>55-60</t>
   </si>
   <si>
     <t>白鲢</t>
@@ -68,7 +68,7 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>10-14.5</t>
+    <t>10-15</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -113,7 +113,7 @@
     <t>青鱼</t>
   </si>
   <si>
-    <t>9-11</t>
+    <t>9.5-11</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +128,7 @@
     <t>黄鳝(养殖)</t>
   </si>
   <si>
-    <t>35-48</t>
+    <t>35-46</t>
   </si>
   <si>
     <t>银鱼</t>
@@ -149,7 +149,7 @@
     <t>牛蛙(养殖)</t>
   </si>
   <si>
-    <t>7.6-8.2</t>
+    <t>6.3-7</t>
   </si>
   <si>
     <t>河鳗(养殖)</t>
@@ -185,9 +185,6 @@
     <t>昂刺鱼</t>
   </si>
   <si>
-    <t>10-17</t>
-  </si>
-  <si>
     <t>清江鱼</t>
   </si>
   <si>
@@ -203,7 +200,7 @@
     <t>河虾(100头)</t>
   </si>
   <si>
-    <t>180</t>
+    <t>260</t>
   </si>
   <si>
     <t>基围虾(大中小)</t>
@@ -215,31 +212,31 @@
     <t>河虾(130头)</t>
   </si>
   <si>
-    <t>153</t>
+    <t>200</t>
   </si>
   <si>
     <t>白虾(大中小)</t>
   </si>
   <si>
-    <t>65-52</t>
+    <t>60-52</t>
   </si>
   <si>
     <t>河虾(150头)</t>
   </si>
   <si>
-    <t>118</t>
+    <t>162</t>
   </si>
   <si>
     <t>罗氏虾(大中小)</t>
   </si>
   <si>
-    <t>43-35-22</t>
+    <t>37-30-24</t>
   </si>
   <si>
     <t>河虾(160头)</t>
   </si>
   <si>
-    <t>95</t>
+    <t>131</t>
   </si>
   <si>
     <t>斑节虾</t>
@@ -248,7 +245,7 @@
     <t>河虾(180头)</t>
   </si>
   <si>
-    <t>76</t>
+    <t>90</t>
   </si>
   <si>
     <t>黑虎虾</t>
@@ -272,25 +269,25 @@
     <t>规格(两)</t>
   </si>
   <si>
-    <t>30-45</t>
+    <t>26-38</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>20-30</t>
+    <t>18-27</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>40-60</t>
+    <t>35-50</t>
   </si>
   <si>
     <t>1.8</t>
   </si>
   <si>
-    <t>50-75</t>
+    <t>45-65</t>
   </si>
   <si>
     <t>3.5</t>
@@ -317,7 +314,7 @@
     <t>7-9青</t>
   </si>
   <si>
-    <t>21-27</t>
+    <t>22-25</t>
   </si>
   <si>
     <t>7-9红</t>
@@ -326,13 +323,16 @@
     <t>4-6青</t>
   </si>
   <si>
-    <t>12-15</t>
+    <t>15-17</t>
   </si>
   <si>
     <t>4-6红</t>
   </si>
   <si>
     <t>3-5</t>
+  </si>
+  <si>
+    <t>12-14</t>
   </si>
 </sst>
 </file>
@@ -2301,7 +2301,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.0" customHeight="true">
+    <row r="1" ht="15.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2311,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="10.0" customHeight="true">
+    <row r="2" ht="11.0" customHeight="true">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="10.0" customHeight="true">
+    <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>56</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" ht="14.0" customHeight="true">
@@ -2634,20 +2634,20 @@
         <v>34</v>
       </c>
       <c r="B20" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>59</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="120"/>
     </row>
     <row r="21" ht="14.0" customHeight="true">
       <c r="A21" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
@@ -2680,19 +2680,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="135" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="136" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" ht="10.0" customHeight="true">
@@ -2700,19 +2700,19 @@
         <v>11</v>
       </c>
       <c r="B24" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="142" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="144" t="s">
         <v>68</v>
-      </c>
-      <c r="F24" s="144" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" ht="14.0" customHeight="true">
@@ -2720,19 +2720,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="147" t="s">
-        <v>71</v>
       </c>
       <c r="D25" s="148" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="150" t="s">
         <v>72</v>
-      </c>
-      <c r="F25" s="150" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" ht="14.0" customHeight="true">
@@ -2740,16 +2740,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="153" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="153" t="s">
-        <v>75</v>
       </c>
       <c r="D26" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="156"/>
     </row>
@@ -2758,24 +2758,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="159" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="159" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="160" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="162" t="s">
         <v>79</v>
-      </c>
-      <c r="F27" s="162" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" ht="14.0" customHeight="true">
       <c r="A28" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="165"/>
@@ -2783,41 +2783,41 @@
       <c r="E28" s="167"/>
       <c r="F28" s="168"/>
     </row>
-    <row r="29" ht="18.0" customHeight="true">
+    <row r="29" ht="19.0" customHeight="true">
       <c r="A29" s="169" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="170" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="171" t="s">
+      <c r="D29" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="172" t="s">
-        <v>84</v>
-      </c>
       <c r="E29" s="173" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="180"/>
     </row>
-    <row r="31" ht="10.0" customHeight="true">
+    <row r="31" ht="14.0" customHeight="true">
       <c r="A31" s="181" t="s">
         <v>6</v>
       </c>
@@ -2825,13 +2825,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="E31" s="185" t="s">
         <v>87</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>88</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2840,13 +2840,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="189" t="s">
+      <c r="D32" s="190" t="s">
         <v>90</v>
-      </c>
-      <c r="D32" s="190" t="s">
-        <v>91</v>
       </c>
       <c r="E32" s="191"/>
       <c r="F32" s="192"/>
@@ -2859,7 +2859,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
@@ -2872,11 +2872,11 @@
         <v>21</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="201"/>
       <c r="D34" s="202" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="204"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="208" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E35" s="209"/>
       <c r="F35" s="210"/>
@@ -2900,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="213"/>
       <c r="D36" s="214" t="s">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C37" s="219"/>
       <c r="D37" s="220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E37" s="221"/>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="14.0" customHeight="true">
+    <row r="38" ht="10.0" customHeight="true">
       <c r="A38" s="223" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="224"/>
       <c r="C38" s="225"/>
@@ -2933,7 +2933,7 @@
       <c r="E38" s="227"/>
       <c r="F38" s="228"/>
     </row>
-    <row r="39" ht="10.0" customHeight="true">
+    <row r="39" ht="14.0" customHeight="true">
       <c r="A39" s="229" t="s">
         <v>3</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="231" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="232"/>
       <c r="E39" s="233" t="s">
@@ -2954,14 +2954,14 @@
         <v>6</v>
       </c>
       <c r="B40" s="236" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="237" t="s">
         <v>99</v>
-      </c>
-      <c r="C40" s="237" t="s">
-        <v>100</v>
       </c>
       <c r="D40" s="238"/>
       <c r="E40" s="239" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" s="240"/>
     </row>
@@ -2970,10 +2970,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="242" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="243" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" s="244"/>
       <c r="E41" s="245"/>
@@ -2984,14 +2984,14 @@
         <v>16</v>
       </c>
       <c r="B42" s="248" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42" s="250"/>
       <c r="E42" s="251" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F42" s="252"/>
     </row>
@@ -3000,10 +3000,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="254" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="255" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="256"/>
       <c r="E43" s="257"/>
@@ -3014,14 +3014,14 @@
         <v>23</v>
       </c>
       <c r="B44" s="260" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" s="261" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" s="262"/>
       <c r="E44" s="263" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="F44" s="264"/>
     </row>
